--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY99"/>
+  <dimension ref="A1:AY101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1616,32 +1616,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126894504</v>
+        <v>126896048</v>
       </c>
       <c r="B11" t="n">
-        <v>92616</v>
+        <v>91587</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>835249</v>
+        <v>835326</v>
       </c>
       <c r="R11" t="n">
-        <v>7431964</v>
+        <v>7431862</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,12 +1701,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1717,32 +1717,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126896048</v>
+        <v>126894504</v>
       </c>
       <c r="B12" t="n">
-        <v>91587</v>
+        <v>92616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>835326</v>
+        <v>835249</v>
       </c>
       <c r="R12" t="n">
-        <v>7431862</v>
+        <v>7431964</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,12 +1802,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1919,32 +1919,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126893108</v>
+        <v>126892879</v>
       </c>
       <c r="B14" t="n">
-        <v>78681</v>
+        <v>98360</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>835380</v>
+        <v>835250</v>
       </c>
       <c r="R14" t="n">
-        <v>7431824</v>
+        <v>7432179</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,12 +2004,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2020,32 +2020,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126892879</v>
+        <v>126893108</v>
       </c>
       <c r="B15" t="n">
-        <v>98360</v>
+        <v>78681</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>835250</v>
+        <v>835380</v>
       </c>
       <c r="R15" t="n">
-        <v>7432179</v>
+        <v>7431824</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,12 +2105,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2232,32 +2232,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126893087</v>
+        <v>126891788</v>
       </c>
       <c r="B17" t="n">
-        <v>97327</v>
+        <v>78681</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>835357</v>
+        <v>835310</v>
       </c>
       <c r="R17" t="n">
-        <v>7432179</v>
+        <v>7431905</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,12 +2317,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2333,32 +2333,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126891788</v>
+        <v>126893087</v>
       </c>
       <c r="B18" t="n">
-        <v>78681</v>
+        <v>97327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>835310</v>
+        <v>835357</v>
       </c>
       <c r="R18" t="n">
-        <v>7431905</v>
+        <v>7432179</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,12 +2418,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -3060,32 +3060,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126896172</v>
+        <v>126896052</v>
       </c>
       <c r="B25" t="n">
-        <v>91587</v>
+        <v>92616</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>835412</v>
+        <v>835305</v>
       </c>
       <c r="R25" t="n">
-        <v>7431868</v>
+        <v>7431987</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,44 +3145,48 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126895020</v>
+        <v>126895047</v>
       </c>
       <c r="B26" t="n">
-        <v>91276</v>
+        <v>92616</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3192,10 +3196,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>835302</v>
+        <v>835325</v>
       </c>
       <c r="R26" t="n">
-        <v>7431967</v>
+        <v>7432027</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3258,32 +3262,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126896052</v>
+        <v>126896172</v>
       </c>
       <c r="B27" t="n">
-        <v>92616</v>
+        <v>91587</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3293,10 +3297,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>835305</v>
+        <v>835412</v>
       </c>
       <c r="R27" t="n">
-        <v>7431987</v>
+        <v>7431868</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3343,48 +3347,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126895047</v>
+        <v>126895020</v>
       </c>
       <c r="B28" t="n">
-        <v>92616</v>
+        <v>91276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>835325</v>
+        <v>835302</v>
       </c>
       <c r="R28" t="n">
-        <v>7432027</v>
+        <v>7431967</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,32 +3571,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126894482</v>
+        <v>126893081</v>
       </c>
       <c r="B30" t="n">
-        <v>97327</v>
+        <v>92620</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>4365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>835253</v>
+        <v>835404</v>
       </c>
       <c r="R30" t="n">
-        <v>7432159</v>
+        <v>7432008</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3656,12 +3656,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3672,10 +3672,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126893081</v>
+        <v>126895037</v>
       </c>
       <c r="B31" t="n">
-        <v>92620</v>
+        <v>91487</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3683,34 +3683,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>835404</v>
+        <v>835296</v>
       </c>
       <c r="R31" t="n">
-        <v>7432008</v>
+        <v>7431963</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3757,12 +3757,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3773,45 +3773,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126895037</v>
+        <v>126894482</v>
       </c>
       <c r="B32" t="n">
-        <v>91487</v>
+        <v>97327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>835296</v>
+        <v>835253</v>
       </c>
       <c r="R32" t="n">
-        <v>7431963</v>
+        <v>7432159</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3858,12 +3858,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4712,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126896015</v>
+        <v>126896012</v>
       </c>
       <c r="B41" t="n">
-        <v>79038</v>
+        <v>97321</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>835346</v>
+        <v>835330</v>
       </c>
       <c r="R41" t="n">
-        <v>7431909</v>
+        <v>7432136</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4813,10 +4813,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126896012</v>
+        <v>126896015</v>
       </c>
       <c r="B42" t="n">
-        <v>97321</v>
+        <v>79038</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4824,21 +4824,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>835330</v>
+        <v>835346</v>
       </c>
       <c r="R42" t="n">
-        <v>7432136</v>
+        <v>7431909</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6277,10 +6277,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126891747</v>
+        <v>126895027</v>
       </c>
       <c r="B56" t="n">
-        <v>80021</v>
+        <v>58027</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6288,34 +6288,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>835247</v>
+        <v>835398</v>
       </c>
       <c r="R56" t="n">
-        <v>7432156</v>
+        <v>7431822</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6362,12 +6362,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6378,32 +6378,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126891218</v>
+        <v>126892870</v>
       </c>
       <c r="B57" t="n">
-        <v>92616</v>
+        <v>57817</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>835411</v>
+        <v>835300</v>
       </c>
       <c r="R57" t="n">
-        <v>7432011</v>
+        <v>7431922</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6463,12 +6463,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6479,45 +6479,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126895019</v>
+        <v>126891218</v>
       </c>
       <c r="B58" t="n">
-        <v>91276</v>
+        <v>92616</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>835295</v>
+        <v>835411</v>
       </c>
       <c r="R58" t="n">
-        <v>7431936</v>
+        <v>7432011</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6564,12 +6564,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6580,10 +6580,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126892867</v>
+        <v>126891747</v>
       </c>
       <c r="B59" t="n">
-        <v>56849</v>
+        <v>80021</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>835268</v>
+        <v>835247</v>
       </c>
       <c r="R59" t="n">
-        <v>7431964</v>
+        <v>7432156</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6653,11 +6653,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6670,12 +6665,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6686,32 +6681,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126895027</v>
+        <v>126895019</v>
       </c>
       <c r="B60" t="n">
-        <v>58027</v>
+        <v>91276</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>112</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6721,10 +6716,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>835398</v>
+        <v>835295</v>
       </c>
       <c r="R60" t="n">
-        <v>7431822</v>
+        <v>7431936</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6787,32 +6782,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892870</v>
+        <v>126892867</v>
       </c>
       <c r="B61" t="n">
-        <v>57817</v>
+        <v>56849</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6822,10 +6817,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>835300</v>
+        <v>835268</v>
       </c>
       <c r="R61" t="n">
-        <v>7431922</v>
+        <v>7431964</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6858,6 +6853,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6989,10 +6989,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126896051</v>
+        <v>126892868</v>
       </c>
       <c r="B63" t="n">
-        <v>98360</v>
+        <v>56849</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7000,21 +7000,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>835330</v>
+        <v>835234</v>
       </c>
       <c r="R63" t="n">
-        <v>7432131</v>
+        <v>7431879</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7062,6 +7062,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7074,12 +7079,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7514,10 +7519,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126892868</v>
+        <v>126896051</v>
       </c>
       <c r="B68" t="n">
-        <v>56849</v>
+        <v>98360</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7525,21 +7530,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7549,10 +7554,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>835234</v>
+        <v>835330</v>
       </c>
       <c r="R68" t="n">
-        <v>7431879</v>
+        <v>7432131</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7587,11 +7592,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7604,12 +7604,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7620,10 +7620,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126915556</v>
+        <v>126915007</v>
       </c>
       <c r="B69" t="n">
-        <v>57817</v>
+        <v>79632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7631,31 +7631,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>835394</v>
+        <v>835444</v>
       </c>
       <c r="R69" t="n">
         <v>7431868</v>
@@ -7705,22 +7705,26 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126915007</v>
+        <v>126915556</v>
       </c>
       <c r="B70" t="n">
-        <v>79632</v>
+        <v>57817</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7728,31 +7732,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>835444</v>
+        <v>835394</v>
       </c>
       <c r="R70" t="n">
         <v>7431868</v>
@@ -7802,19 +7806,15 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8117,45 +8117,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126915568</v>
+        <v>126894632</v>
       </c>
       <c r="B74" t="n">
-        <v>92616</v>
+        <v>92809</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>835341</v>
+        <v>835406</v>
       </c>
       <c r="R74" t="n">
-        <v>7432052</v>
+        <v>7431965</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8202,57 +8202,61 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126894632</v>
+        <v>126915568</v>
       </c>
       <c r="B75" t="n">
-        <v>92809</v>
+        <v>92616</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>835406</v>
+        <v>835341</v>
       </c>
       <c r="R75" t="n">
-        <v>7431965</v>
+        <v>7432052</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8299,19 +8303,15 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8513,10 +8513,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126915011</v>
+        <v>126894633</v>
       </c>
       <c r="B78" t="n">
-        <v>91276</v>
+        <v>78773</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8524,21 +8524,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>112</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>835374</v>
+        <v>835411</v>
       </c>
       <c r="R78" t="n">
-        <v>7432212</v>
+        <v>7431972</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8598,12 +8598,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8614,10 +8614,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126915032</v>
+        <v>126915011</v>
       </c>
       <c r="B79" t="n">
-        <v>78420</v>
+        <v>91276</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8625,21 +8625,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6437</v>
+        <v>112</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>835212</v>
+        <v>835374</v>
       </c>
       <c r="R79" t="n">
-        <v>7432119</v>
+        <v>7432212</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126894633</v>
+        <v>126915032</v>
       </c>
       <c r="B80" t="n">
-        <v>78773</v>
+        <v>78420</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>835411</v>
+        <v>835212</v>
       </c>
       <c r="R80" t="n">
-        <v>7431972</v>
+        <v>7432119</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8800,12 +8800,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9854,32 +9854,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126943156</v>
+        <v>126943157</v>
       </c>
       <c r="B91" t="n">
-        <v>92616</v>
+        <v>77992</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>835445</v>
+        <v>835394</v>
       </c>
       <c r="R91" t="n">
-        <v>7431908</v>
+        <v>7431928</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9955,32 +9955,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126943157</v>
+        <v>126943156</v>
       </c>
       <c r="B92" t="n">
-        <v>77992</v>
+        <v>92616</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>835394</v>
+        <v>835445</v>
       </c>
       <c r="R92" t="n">
-        <v>7431928</v>
+        <v>7431908</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10770,6 +10770,218 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>127414787</v>
+      </c>
+      <c r="B100" t="n">
+        <v>92610</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Limingoån, Nb</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>835307</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7432078</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127414788</v>
+      </c>
+      <c r="B101" t="n">
+        <v>92608</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Limingoån, Nb</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>835310</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7432075</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -1414,32 +1414,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126896034</v>
+        <v>126893109</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>835299</v>
+        <v>835379</v>
       </c>
       <c r="R9" t="n">
-        <v>7432168</v>
+        <v>7431868</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,12 +1499,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1515,32 +1515,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126893109</v>
+        <v>126896034</v>
       </c>
       <c r="B10" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>835379</v>
+        <v>835299</v>
       </c>
       <c r="R10" t="n">
-        <v>7431868</v>
+        <v>7432168</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,12 +1600,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1818,45 +1818,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126895046</v>
+        <v>126893108</v>
       </c>
       <c r="B13" t="n">
-        <v>92616</v>
+        <v>78681</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>835398</v>
+        <v>835380</v>
       </c>
       <c r="R13" t="n">
-        <v>7431830</v>
+        <v>7431824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,12 +1903,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126892879</v>
+        <v>126895046</v>
       </c>
       <c r="B14" t="n">
-        <v>98360</v>
+        <v>92616</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,34 +1930,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>835250</v>
+        <v>835398</v>
       </c>
       <c r="R14" t="n">
-        <v>7432179</v>
+        <v>7431830</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,12 +2004,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2020,32 +2020,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126893108</v>
+        <v>126892879</v>
       </c>
       <c r="B15" t="n">
-        <v>78681</v>
+        <v>98360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>835380</v>
+        <v>835250</v>
       </c>
       <c r="R15" t="n">
-        <v>7431824</v>
+        <v>7432179</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,12 +2105,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2747,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126891211</v>
+        <v>126896462</v>
       </c>
       <c r="B22" t="n">
-        <v>91276</v>
+        <v>78772</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2758,21 +2758,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>835367</v>
+        <v>835438</v>
       </c>
       <c r="R22" t="n">
-        <v>7432211</v>
+        <v>7431930</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,9 +2815,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2832,12 +2842,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2848,10 +2858,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126896462</v>
+        <v>126891737</v>
       </c>
       <c r="B23" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,21 +2869,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2883,10 +2893,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>835438</v>
+        <v>835163</v>
       </c>
       <c r="R23" t="n">
-        <v>7431930</v>
+        <v>7431931</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2916,19 +2926,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2943,12 +2943,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891737</v>
+        <v>126891211</v>
       </c>
       <c r="B24" t="n">
-        <v>79632</v>
+        <v>91276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>835163</v>
+        <v>835367</v>
       </c>
       <c r="R24" t="n">
-        <v>7431931</v>
+        <v>7432211</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3044,12 +3044,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3060,45 +3060,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126896052</v>
+        <v>126895020</v>
       </c>
       <c r="B25" t="n">
-        <v>92616</v>
+        <v>91276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>112</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>835305</v>
+        <v>835302</v>
       </c>
       <c r="R25" t="n">
-        <v>7431987</v>
+        <v>7431967</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,12 +3145,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3161,45 +3161,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126895047</v>
+        <v>126896172</v>
       </c>
       <c r="B26" t="n">
-        <v>92616</v>
+        <v>91587</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>835325</v>
+        <v>835412</v>
       </c>
       <c r="R26" t="n">
-        <v>7432027</v>
+        <v>7431868</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3246,48 +3246,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126896172</v>
+        <v>126896052</v>
       </c>
       <c r="B27" t="n">
-        <v>91587</v>
+        <v>92616</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3297,10 +3293,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>835412</v>
+        <v>835305</v>
       </c>
       <c r="R27" t="n">
-        <v>7431868</v>
+        <v>7431987</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,44 +3343,48 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126895020</v>
+        <v>126895047</v>
       </c>
       <c r="B28" t="n">
-        <v>91276</v>
+        <v>92616</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>835302</v>
+        <v>835325</v>
       </c>
       <c r="R28" t="n">
-        <v>7431967</v>
+        <v>7432027</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,10 +3571,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126893081</v>
+        <v>126895037</v>
       </c>
       <c r="B30" t="n">
-        <v>92620</v>
+        <v>91487</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3582,34 +3582,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>835404</v>
+        <v>835296</v>
       </c>
       <c r="R30" t="n">
-        <v>7432008</v>
+        <v>7431963</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3656,12 +3656,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3672,10 +3672,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126895037</v>
+        <v>126893081</v>
       </c>
       <c r="B31" t="n">
-        <v>91487</v>
+        <v>92620</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3683,34 +3683,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>835296</v>
+        <v>835404</v>
       </c>
       <c r="R31" t="n">
-        <v>7431963</v>
+        <v>7432008</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3757,12 +3757,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3874,32 +3874,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126891743</v>
+        <v>126893092</v>
       </c>
       <c r="B33" t="n">
-        <v>91346</v>
+        <v>97327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>835324</v>
+        <v>835234</v>
       </c>
       <c r="R33" t="n">
-        <v>7431890</v>
+        <v>7432287</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3959,12 +3959,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4076,10 +4076,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126896454</v>
+        <v>126891743</v>
       </c>
       <c r="B35" t="n">
-        <v>79632</v>
+        <v>91346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4087,21 +4087,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>835391</v>
+        <v>835324</v>
       </c>
       <c r="R35" t="n">
-        <v>7431880</v>
+        <v>7431890</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4144,19 +4144,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4171,12 +4161,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4298,32 +4288,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126893092</v>
+        <v>126896454</v>
       </c>
       <c r="B37" t="n">
-        <v>97327</v>
+        <v>79632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4333,10 +4323,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>835234</v>
+        <v>835391</v>
       </c>
       <c r="R37" t="n">
-        <v>7432287</v>
+        <v>7431880</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4366,9 +4356,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4383,12 +4383,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4712,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126896012</v>
+        <v>126896015</v>
       </c>
       <c r="B41" t="n">
-        <v>97321</v>
+        <v>79038</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>835330</v>
+        <v>835346</v>
       </c>
       <c r="R41" t="n">
-        <v>7432136</v>
+        <v>7431909</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4813,10 +4813,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126896015</v>
+        <v>126896012</v>
       </c>
       <c r="B42" t="n">
-        <v>79038</v>
+        <v>97321</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4824,21 +4824,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>835346</v>
+        <v>835330</v>
       </c>
       <c r="R42" t="n">
-        <v>7431909</v>
+        <v>7432136</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4914,32 +4914,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126896215</v>
+        <v>126892874</v>
       </c>
       <c r="B43" t="n">
-        <v>95300</v>
+        <v>75138</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2387</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>835224</v>
+        <v>835180</v>
       </c>
       <c r="R43" t="n">
-        <v>7431834</v>
+        <v>7431962</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4982,19 +4982,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5009,12 +4999,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5025,32 +5015,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126896207</v>
+        <v>126896215</v>
       </c>
       <c r="B44" t="n">
-        <v>79632</v>
+        <v>95300</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>2387</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5060,10 +5050,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>835216</v>
+        <v>835224</v>
       </c>
       <c r="R44" t="n">
-        <v>7432256</v>
+        <v>7431834</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5095,7 +5085,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5105,7 +5095,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5136,10 +5126,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126892874</v>
+        <v>126896207</v>
       </c>
       <c r="B45" t="n">
-        <v>75138</v>
+        <v>79632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5147,21 +5137,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5171,10 +5161,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>835180</v>
+        <v>835216</v>
       </c>
       <c r="R45" t="n">
-        <v>7431962</v>
+        <v>7432256</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5204,9 +5194,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5221,12 +5221,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5338,10 +5338,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126891762</v>
+        <v>126896013</v>
       </c>
       <c r="B47" t="n">
-        <v>105478</v>
+        <v>97327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>835361</v>
+        <v>835330</v>
       </c>
       <c r="R47" t="n">
-        <v>7431869</v>
+        <v>7431947</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5423,12 +5423,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5439,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126896013</v>
+        <v>126891762</v>
       </c>
       <c r="B48" t="n">
-        <v>97327</v>
+        <v>105478</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5450,21 +5450,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>835330</v>
+        <v>835361</v>
       </c>
       <c r="R48" t="n">
-        <v>7431947</v>
+        <v>7431869</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,12 +5524,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5863,45 +5863,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126893083</v>
+        <v>126895028</v>
       </c>
       <c r="B52" t="n">
-        <v>97321</v>
+        <v>91254</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>2013</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>835458</v>
+        <v>835423</v>
       </c>
       <c r="R52" t="n">
-        <v>7431881</v>
+        <v>7431886</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5948,12 +5948,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5964,45 +5964,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126895028</v>
+        <v>126893090</v>
       </c>
       <c r="B53" t="n">
-        <v>91254</v>
+        <v>92608</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2013</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>835423</v>
+        <v>835354</v>
       </c>
       <c r="R53" t="n">
-        <v>7431886</v>
+        <v>7431995</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6049,12 +6049,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6065,10 +6065,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126893090</v>
+        <v>126896455</v>
       </c>
       <c r="B54" t="n">
-        <v>92608</v>
+        <v>79632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6076,21 +6076,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>835354</v>
+        <v>835445</v>
       </c>
       <c r="R54" t="n">
-        <v>7431995</v>
+        <v>7431926</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6133,9 +6133,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6150,12 +6160,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6166,32 +6176,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126896455</v>
+        <v>126893083</v>
       </c>
       <c r="B55" t="n">
-        <v>79632</v>
+        <v>97321</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6201,10 +6211,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>835445</v>
+        <v>835458</v>
       </c>
       <c r="R55" t="n">
-        <v>7431926</v>
+        <v>7431881</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6234,19 +6244,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6261,12 +6261,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6277,32 +6277,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126895027</v>
+        <v>126895019</v>
       </c>
       <c r="B56" t="n">
-        <v>58027</v>
+        <v>91276</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>112</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>835398</v>
+        <v>835295</v>
       </c>
       <c r="R56" t="n">
-        <v>7431822</v>
+        <v>7431936</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6378,32 +6378,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126892870</v>
+        <v>126892867</v>
       </c>
       <c r="B57" t="n">
-        <v>57817</v>
+        <v>56849</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>835300</v>
+        <v>835268</v>
       </c>
       <c r="R57" t="n">
-        <v>7431922</v>
+        <v>7431964</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6449,6 +6449,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6479,10 +6484,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126891218</v>
+        <v>126895027</v>
       </c>
       <c r="B58" t="n">
-        <v>92616</v>
+        <v>58027</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6490,34 +6495,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>835411</v>
+        <v>835398</v>
       </c>
       <c r="R58" t="n">
-        <v>7432011</v>
+        <v>7431822</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6564,12 +6569,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6580,32 +6585,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126891747</v>
+        <v>126896035</v>
       </c>
       <c r="B59" t="n">
-        <v>80021</v>
+        <v>98443</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6615,10 +6620,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>835247</v>
+        <v>835290</v>
       </c>
       <c r="R59" t="n">
-        <v>7432156</v>
+        <v>7432175</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6665,12 +6670,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6681,45 +6686,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126895019</v>
+        <v>126891218</v>
       </c>
       <c r="B60" t="n">
-        <v>91276</v>
+        <v>92616</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>835295</v>
+        <v>835411</v>
       </c>
       <c r="R60" t="n">
-        <v>7431936</v>
+        <v>7432011</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6766,12 +6771,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6782,10 +6787,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892867</v>
+        <v>126891747</v>
       </c>
       <c r="B61" t="n">
-        <v>56849</v>
+        <v>80021</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6793,21 +6798,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6817,10 +6822,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>835268</v>
+        <v>835247</v>
       </c>
       <c r="R61" t="n">
-        <v>7431964</v>
+        <v>7432156</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6855,11 +6860,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6872,12 +6872,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6888,32 +6888,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126896035</v>
+        <v>126892870</v>
       </c>
       <c r="B62" t="n">
-        <v>98443</v>
+        <v>57817</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6923,10 +6923,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>835290</v>
+        <v>835300</v>
       </c>
       <c r="R62" t="n">
-        <v>7432175</v>
+        <v>7431922</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6973,12 +6973,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6989,10 +6989,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126892868</v>
+        <v>126896213</v>
       </c>
       <c r="B63" t="n">
-        <v>56849</v>
+        <v>100598</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7000,21 +7000,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>1365</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>835234</v>
+        <v>835235</v>
       </c>
       <c r="R63" t="n">
-        <v>7431879</v>
+        <v>7431827</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7057,14 +7057,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7079,12 +7084,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7095,32 +7100,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126894487</v>
+        <v>126894490</v>
       </c>
       <c r="B64" t="n">
-        <v>56840</v>
+        <v>91487</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102612</v>
+        <v>1503</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7130,10 +7135,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>835105</v>
+        <v>835300</v>
       </c>
       <c r="R64" t="n">
-        <v>7432062</v>
+        <v>7431907</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7196,32 +7201,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126894490</v>
+        <v>126894487</v>
       </c>
       <c r="B65" t="n">
-        <v>91487</v>
+        <v>56840</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1503</v>
+        <v>102612</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7231,10 +7236,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>835300</v>
+        <v>835105</v>
       </c>
       <c r="R65" t="n">
-        <v>7431907</v>
+        <v>7432062</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7297,32 +7302,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126896458</v>
+        <v>126896051</v>
       </c>
       <c r="B66" t="n">
-        <v>91276</v>
+        <v>98360</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>112</v>
+        <v>219790</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7332,10 +7337,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>835425</v>
+        <v>835330</v>
       </c>
       <c r="R66" t="n">
-        <v>7431979</v>
+        <v>7432131</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7365,19 +7370,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7392,12 +7387,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7408,32 +7403,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126896213</v>
+        <v>126896458</v>
       </c>
       <c r="B67" t="n">
-        <v>100598</v>
+        <v>91276</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1365</v>
+        <v>112</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7443,10 +7438,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>835235</v>
+        <v>835425</v>
       </c>
       <c r="R67" t="n">
-        <v>7431827</v>
+        <v>7431979</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7478,7 +7473,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7488,7 +7483,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7508,7 +7503,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7519,10 +7514,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126896051</v>
+        <v>126892868</v>
       </c>
       <c r="B68" t="n">
-        <v>98360</v>
+        <v>56849</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7530,21 +7525,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7554,10 +7549,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>835330</v>
+        <v>835234</v>
       </c>
       <c r="R68" t="n">
-        <v>7432131</v>
+        <v>7431879</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7592,6 +7587,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7604,12 +7604,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8016,7 +8016,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126915019</v>
+        <v>126894632</v>
       </c>
       <c r="B73" t="n">
         <v>92809</v>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>835275</v>
+        <v>835406</v>
       </c>
       <c r="R73" t="n">
-        <v>7432030</v>
+        <v>7431965</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8101,12 +8101,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8117,45 +8117,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126894632</v>
+        <v>126915568</v>
       </c>
       <c r="B74" t="n">
-        <v>92809</v>
+        <v>92616</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>835406</v>
+        <v>835341</v>
       </c>
       <c r="R74" t="n">
-        <v>7431965</v>
+        <v>7432052</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8202,61 +8202,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126915568</v>
+        <v>126915019</v>
       </c>
       <c r="B75" t="n">
-        <v>92616</v>
+        <v>92809</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>835341</v>
+        <v>835275</v>
       </c>
       <c r="R75" t="n">
-        <v>7432052</v>
+        <v>7432030</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8303,15 +8299,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8513,10 +8513,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126894633</v>
+        <v>126915011</v>
       </c>
       <c r="B78" t="n">
-        <v>78773</v>
+        <v>91276</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8524,21 +8524,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>112</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>835411</v>
+        <v>835374</v>
       </c>
       <c r="R78" t="n">
-        <v>7431972</v>
+        <v>7432212</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8598,12 +8598,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8614,10 +8614,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126915011</v>
+        <v>126915032</v>
       </c>
       <c r="B79" t="n">
-        <v>91276</v>
+        <v>78420</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8625,21 +8625,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>112</v>
+        <v>6437</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>835374</v>
+        <v>835212</v>
       </c>
       <c r="R79" t="n">
-        <v>7432212</v>
+        <v>7432119</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126915032</v>
+        <v>126894633</v>
       </c>
       <c r="B80" t="n">
-        <v>78420</v>
+        <v>78773</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>835212</v>
+        <v>835411</v>
       </c>
       <c r="R80" t="n">
-        <v>7432119</v>
+        <v>7431972</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8800,12 +8800,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9854,32 +9854,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126943157</v>
+        <v>126943156</v>
       </c>
       <c r="B91" t="n">
-        <v>77992</v>
+        <v>92616</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>835394</v>
+        <v>835445</v>
       </c>
       <c r="R91" t="n">
-        <v>7431928</v>
+        <v>7431908</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9955,32 +9955,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126943156</v>
+        <v>126943157</v>
       </c>
       <c r="B92" t="n">
-        <v>92616</v>
+        <v>77992</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>835445</v>
+        <v>835394</v>
       </c>
       <c r="R92" t="n">
-        <v>7431908</v>
+        <v>7431928</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10571,32 +10571,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126943151</v>
+        <v>126943153</v>
       </c>
       <c r="B98" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>835382</v>
+        <v>835440</v>
       </c>
       <c r="R98" t="n">
-        <v>7432189</v>
+        <v>7431856</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10672,32 +10672,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126943153</v>
+        <v>126943151</v>
       </c>
       <c r="B99" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>835440</v>
+        <v>835382</v>
       </c>
       <c r="R99" t="n">
-        <v>7431856</v>
+        <v>7432189</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -2121,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126896456</v>
+        <v>126891788</v>
       </c>
       <c r="B16" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,21 +2132,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>835435</v>
+        <v>835310</v>
       </c>
       <c r="R16" t="n">
-        <v>7431927</v>
+        <v>7431905</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,19 +2189,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2216,12 +2206,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2232,32 +2222,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126891788</v>
+        <v>126893087</v>
       </c>
       <c r="B17" t="n">
-        <v>78681</v>
+        <v>97327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2267,10 +2257,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>835310</v>
+        <v>835357</v>
       </c>
       <c r="R17" t="n">
-        <v>7431905</v>
+        <v>7432179</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,12 +2307,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2333,32 +2323,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126893087</v>
+        <v>126896456</v>
       </c>
       <c r="B18" t="n">
-        <v>97327</v>
+        <v>79632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2368,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>835357</v>
+        <v>835435</v>
       </c>
       <c r="R18" t="n">
-        <v>7432179</v>
+        <v>7431927</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2401,9 +2391,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,12 +2418,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2434,32 +2434,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126896010</v>
+        <v>126891745</v>
       </c>
       <c r="B19" t="n">
-        <v>56592</v>
+        <v>91276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208255</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>835133</v>
+        <v>835271</v>
       </c>
       <c r="R19" t="n">
-        <v>7432014</v>
+        <v>7431952</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2519,12 +2519,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2535,32 +2535,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126891745</v>
+        <v>126896208</v>
       </c>
       <c r="B20" t="n">
-        <v>91276</v>
+        <v>97327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>112</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>835271</v>
+        <v>835253</v>
       </c>
       <c r="R20" t="n">
-        <v>7431952</v>
+        <v>7431988</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2603,9 +2603,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2620,12 +2630,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2636,10 +2646,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126896208</v>
+        <v>126896010</v>
       </c>
       <c r="B21" t="n">
-        <v>97327</v>
+        <v>56592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2647,21 +2657,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>208255</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2671,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>835253</v>
+        <v>835133</v>
       </c>
       <c r="R21" t="n">
-        <v>7431988</v>
+        <v>7432014</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,19 +2714,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2731,12 +2731,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2747,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126896462</v>
+        <v>126891211</v>
       </c>
       <c r="B22" t="n">
-        <v>78772</v>
+        <v>91276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2758,21 +2758,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>112</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>835438</v>
+        <v>835367</v>
       </c>
       <c r="R22" t="n">
-        <v>7431930</v>
+        <v>7432211</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,19 +2815,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2842,12 +2832,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2858,10 +2848,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126891737</v>
+        <v>126896462</v>
       </c>
       <c r="B23" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2869,21 +2859,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2893,10 +2883,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>835163</v>
+        <v>835438</v>
       </c>
       <c r="R23" t="n">
-        <v>7431931</v>
+        <v>7431930</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2926,9 +2916,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2943,12 +2943,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891211</v>
+        <v>126891737</v>
       </c>
       <c r="B24" t="n">
-        <v>91276</v>
+        <v>79632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>112</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>835367</v>
+        <v>835163</v>
       </c>
       <c r="R24" t="n">
-        <v>7432211</v>
+        <v>7431931</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3044,12 +3044,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3874,32 +3874,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126893092</v>
+        <v>126896220</v>
       </c>
       <c r="B33" t="n">
-        <v>97327</v>
+        <v>82855</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>835234</v>
+        <v>835166</v>
       </c>
       <c r="R33" t="n">
-        <v>7432287</v>
+        <v>7431954</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,9 +3942,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3959,12 +3969,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4177,10 +4187,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126896220</v>
+        <v>126896454</v>
       </c>
       <c r="B36" t="n">
-        <v>82855</v>
+        <v>79632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4188,21 +4198,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4212,10 +4222,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>835166</v>
+        <v>835391</v>
       </c>
       <c r="R36" t="n">
-        <v>7431954</v>
+        <v>7431880</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,7 +4257,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4257,7 +4267,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4277,7 +4287,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4288,32 +4298,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126896454</v>
+        <v>126893092</v>
       </c>
       <c r="B37" t="n">
-        <v>79632</v>
+        <v>97327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4323,10 +4333,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>835391</v>
+        <v>835234</v>
       </c>
       <c r="R37" t="n">
-        <v>7431880</v>
+        <v>7432287</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,19 +4366,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4383,12 +4383,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -5338,10 +5338,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126896013</v>
+        <v>126891762</v>
       </c>
       <c r="B47" t="n">
-        <v>97327</v>
+        <v>105478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>835330</v>
+        <v>835361</v>
       </c>
       <c r="R47" t="n">
-        <v>7431947</v>
+        <v>7431869</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5423,12 +5423,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5439,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126891762</v>
+        <v>126896013</v>
       </c>
       <c r="B48" t="n">
-        <v>105478</v>
+        <v>97327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5450,21 +5450,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>835361</v>
+        <v>835330</v>
       </c>
       <c r="R48" t="n">
-        <v>7431869</v>
+        <v>7431947</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,12 +5524,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -8117,45 +8117,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126915568</v>
+        <v>126915019</v>
       </c>
       <c r="B74" t="n">
-        <v>92616</v>
+        <v>92809</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>835341</v>
+        <v>835275</v>
       </c>
       <c r="R74" t="n">
-        <v>7432052</v>
+        <v>7432030</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8202,57 +8202,61 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126915019</v>
+        <v>126915568</v>
       </c>
       <c r="B75" t="n">
-        <v>92809</v>
+        <v>92616</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>835275</v>
+        <v>835341</v>
       </c>
       <c r="R75" t="n">
-        <v>7432030</v>
+        <v>7432052</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8299,19 +8303,15 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -1818,32 +1818,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126893108</v>
+        <v>126892879</v>
       </c>
       <c r="B13" t="n">
-        <v>78681</v>
+        <v>98360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>835380</v>
+        <v>835250</v>
       </c>
       <c r="R13" t="n">
-        <v>7431824</v>
+        <v>7432179</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,12 +1903,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2020,32 +2020,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126892879</v>
+        <v>126893108</v>
       </c>
       <c r="B15" t="n">
-        <v>98360</v>
+        <v>78681</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>835250</v>
+        <v>835380</v>
       </c>
       <c r="R15" t="n">
-        <v>7432179</v>
+        <v>7431824</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,12 +2105,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2121,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126891788</v>
+        <v>126896456</v>
       </c>
       <c r="B16" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,21 +2132,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>835310</v>
+        <v>835435</v>
       </c>
       <c r="R16" t="n">
-        <v>7431905</v>
+        <v>7431927</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,9 +2189,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2206,12 +2216,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2222,32 +2232,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126893087</v>
+        <v>126891788</v>
       </c>
       <c r="B17" t="n">
-        <v>97327</v>
+        <v>78681</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2257,10 +2267,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>835357</v>
+        <v>835310</v>
       </c>
       <c r="R17" t="n">
-        <v>7432179</v>
+        <v>7431905</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,12 +2317,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2323,32 +2333,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126896456</v>
+        <v>126893087</v>
       </c>
       <c r="B18" t="n">
-        <v>79632</v>
+        <v>97327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2358,10 +2368,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>835435</v>
+        <v>835357</v>
       </c>
       <c r="R18" t="n">
-        <v>7431927</v>
+        <v>7432179</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2391,19 +2401,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,12 +2418,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2747,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126891211</v>
+        <v>126896462</v>
       </c>
       <c r="B22" t="n">
-        <v>91276</v>
+        <v>78772</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2758,21 +2758,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>835367</v>
+        <v>835438</v>
       </c>
       <c r="R22" t="n">
-        <v>7432211</v>
+        <v>7431930</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,9 +2815,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2832,12 +2842,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2848,10 +2858,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126896462</v>
+        <v>126891737</v>
       </c>
       <c r="B23" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,21 +2869,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2883,10 +2893,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>835438</v>
+        <v>835163</v>
       </c>
       <c r="R23" t="n">
-        <v>7431930</v>
+        <v>7431931</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2916,19 +2926,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2943,12 +2943,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891737</v>
+        <v>126891211</v>
       </c>
       <c r="B24" t="n">
-        <v>79632</v>
+        <v>91276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>835163</v>
+        <v>835367</v>
       </c>
       <c r="R24" t="n">
-        <v>7431931</v>
+        <v>7432211</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3044,12 +3044,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3060,45 +3060,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126895020</v>
+        <v>126896052</v>
       </c>
       <c r="B25" t="n">
-        <v>91276</v>
+        <v>92616</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>835302</v>
+        <v>835305</v>
       </c>
       <c r="R25" t="n">
-        <v>7431967</v>
+        <v>7431987</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,12 +3145,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3161,45 +3161,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126896172</v>
+        <v>126895047</v>
       </c>
       <c r="B26" t="n">
-        <v>91587</v>
+        <v>92616</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>835412</v>
+        <v>835325</v>
       </c>
       <c r="R26" t="n">
-        <v>7431868</v>
+        <v>7432027</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3246,44 +3246,48 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126896052</v>
+        <v>126896216</v>
       </c>
       <c r="B27" t="n">
-        <v>92616</v>
+        <v>57817</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3293,10 +3297,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>835305</v>
+        <v>835232</v>
       </c>
       <c r="R27" t="n">
-        <v>7431987</v>
+        <v>7431857</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,9 +3330,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3343,12 +3357,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3359,32 +3373,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126895047</v>
+        <v>126895020</v>
       </c>
       <c r="B28" t="n">
-        <v>92616</v>
+        <v>91276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3394,10 +3408,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>835325</v>
+        <v>835302</v>
       </c>
       <c r="R28" t="n">
-        <v>7432027</v>
+        <v>7431967</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3460,32 +3474,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126896216</v>
+        <v>126896172</v>
       </c>
       <c r="B29" t="n">
-        <v>57817</v>
+        <v>91587</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>65</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3495,10 +3509,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>835232</v>
+        <v>835412</v>
       </c>
       <c r="R29" t="n">
-        <v>7431857</v>
+        <v>7431868</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3528,19 +3542,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3555,19 +3559,15 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5338,10 +5338,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126891762</v>
+        <v>126896013</v>
       </c>
       <c r="B47" t="n">
-        <v>105478</v>
+        <v>97327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>835361</v>
+        <v>835330</v>
       </c>
       <c r="R47" t="n">
-        <v>7431869</v>
+        <v>7431947</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5423,12 +5423,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5439,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126896013</v>
+        <v>126891762</v>
       </c>
       <c r="B48" t="n">
-        <v>97327</v>
+        <v>105478</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5450,21 +5450,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>835330</v>
+        <v>835361</v>
       </c>
       <c r="R48" t="n">
-        <v>7431947</v>
+        <v>7431869</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,12 +5524,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5762,10 +5762,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126896046</v>
+        <v>126893090</v>
       </c>
       <c r="B51" t="n">
-        <v>82855</v>
+        <v>92608</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5773,21 +5773,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>4361</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5797,10 +5797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>835241</v>
+        <v>835354</v>
       </c>
       <c r="R51" t="n">
-        <v>7432287</v>
+        <v>7431995</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5847,12 +5847,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5863,45 +5863,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126895028</v>
+        <v>126896455</v>
       </c>
       <c r="B52" t="n">
-        <v>91254</v>
+        <v>79632</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2013</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>835423</v>
+        <v>835445</v>
       </c>
       <c r="R52" t="n">
-        <v>7431886</v>
+        <v>7431926</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5931,9 +5931,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5948,12 +5958,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5964,32 +5974,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126893090</v>
+        <v>126893083</v>
       </c>
       <c r="B53" t="n">
-        <v>92608</v>
+        <v>97321</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5999,10 +6009,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>835354</v>
+        <v>835458</v>
       </c>
       <c r="R53" t="n">
-        <v>7431995</v>
+        <v>7431881</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6065,10 +6075,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126896455</v>
+        <v>126896046</v>
       </c>
       <c r="B54" t="n">
-        <v>79632</v>
+        <v>82855</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6076,21 +6086,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6100,10 +6110,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>835445</v>
+        <v>835241</v>
       </c>
       <c r="R54" t="n">
-        <v>7431926</v>
+        <v>7432287</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6133,19 +6143,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6160,12 +6160,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6176,45 +6176,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893083</v>
+        <v>126895028</v>
       </c>
       <c r="B55" t="n">
-        <v>97321</v>
+        <v>91254</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>2013</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>835458</v>
+        <v>835423</v>
       </c>
       <c r="R55" t="n">
-        <v>7431881</v>
+        <v>7431886</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6261,12 +6261,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6277,45 +6277,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126895019</v>
+        <v>126891218</v>
       </c>
       <c r="B56" t="n">
-        <v>91276</v>
+        <v>92616</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>835295</v>
+        <v>835411</v>
       </c>
       <c r="R56" t="n">
-        <v>7431936</v>
+        <v>7432011</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6362,12 +6362,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6378,45 +6378,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126892867</v>
+        <v>126895019</v>
       </c>
       <c r="B57" t="n">
-        <v>56849</v>
+        <v>91276</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>112</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>835268</v>
+        <v>835295</v>
       </c>
       <c r="R57" t="n">
-        <v>7431964</v>
+        <v>7431936</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6451,11 +6451,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6468,12 +6463,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6484,10 +6479,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126895027</v>
+        <v>126891747</v>
       </c>
       <c r="B58" t="n">
-        <v>58027</v>
+        <v>80021</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6495,34 +6490,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>6456</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>835398</v>
+        <v>835247</v>
       </c>
       <c r="R58" t="n">
-        <v>7431822</v>
+        <v>7432156</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6569,12 +6564,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6585,32 +6580,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126896035</v>
+        <v>126892867</v>
       </c>
       <c r="B59" t="n">
-        <v>98443</v>
+        <v>56849</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6620,10 +6615,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>835290</v>
+        <v>835268</v>
       </c>
       <c r="R59" t="n">
-        <v>7432175</v>
+        <v>7431964</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6658,6 +6653,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6670,12 +6670,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6686,10 +6686,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126891218</v>
+        <v>126895027</v>
       </c>
       <c r="B60" t="n">
-        <v>92616</v>
+        <v>58027</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6697,34 +6697,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>835411</v>
+        <v>835398</v>
       </c>
       <c r="R60" t="n">
-        <v>7432011</v>
+        <v>7431822</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6771,12 +6771,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6787,32 +6787,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126891747</v>
+        <v>126892870</v>
       </c>
       <c r="B61" t="n">
-        <v>80021</v>
+        <v>57817</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>835247</v>
+        <v>835300</v>
       </c>
       <c r="R61" t="n">
-        <v>7432156</v>
+        <v>7431922</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6872,12 +6872,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6888,32 +6888,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126892870</v>
+        <v>126896035</v>
       </c>
       <c r="B62" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6923,10 +6923,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>835300</v>
+        <v>835290</v>
       </c>
       <c r="R62" t="n">
-        <v>7431922</v>
+        <v>7432175</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6973,12 +6973,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6989,32 +6989,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126896213</v>
+        <v>126896458</v>
       </c>
       <c r="B63" t="n">
-        <v>100598</v>
+        <v>91276</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1365</v>
+        <v>112</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>835235</v>
+        <v>835425</v>
       </c>
       <c r="R63" t="n">
-        <v>7431827</v>
+        <v>7431979</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7100,32 +7100,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126894490</v>
+        <v>126896213</v>
       </c>
       <c r="B64" t="n">
-        <v>91487</v>
+        <v>100598</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1503</v>
+        <v>1365</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>835300</v>
+        <v>835235</v>
       </c>
       <c r="R64" t="n">
-        <v>7431907</v>
+        <v>7431827</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7168,9 +7168,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7185,12 +7195,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7201,32 +7211,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126894487</v>
+        <v>126894490</v>
       </c>
       <c r="B65" t="n">
-        <v>56840</v>
+        <v>91487</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102612</v>
+        <v>1503</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7236,10 +7246,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>835105</v>
+        <v>835300</v>
       </c>
       <c r="R65" t="n">
-        <v>7432062</v>
+        <v>7431907</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7302,10 +7312,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126896051</v>
+        <v>126892868</v>
       </c>
       <c r="B66" t="n">
-        <v>98360</v>
+        <v>56849</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7313,21 +7323,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7337,10 +7347,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>835330</v>
+        <v>835234</v>
       </c>
       <c r="R66" t="n">
-        <v>7432131</v>
+        <v>7431879</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7375,6 +7385,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7387,12 +7402,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7403,10 +7418,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126896458</v>
+        <v>126894487</v>
       </c>
       <c r="B67" t="n">
-        <v>91276</v>
+        <v>56840</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7414,21 +7429,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>112</v>
+        <v>102612</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7438,10 +7453,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>835425</v>
+        <v>835105</v>
       </c>
       <c r="R67" t="n">
-        <v>7431979</v>
+        <v>7432062</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7471,19 +7486,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7498,12 +7503,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7514,10 +7519,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126892868</v>
+        <v>126896051</v>
       </c>
       <c r="B68" t="n">
-        <v>56849</v>
+        <v>98360</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7525,21 +7530,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7549,10 +7554,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>835234</v>
+        <v>835330</v>
       </c>
       <c r="R68" t="n">
-        <v>7431879</v>
+        <v>7432131</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7587,11 +7592,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7604,12 +7604,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7620,10 +7620,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126915007</v>
+        <v>126915556</v>
       </c>
       <c r="B69" t="n">
-        <v>79632</v>
+        <v>57817</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7631,31 +7631,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>835444</v>
+        <v>835394</v>
       </c>
       <c r="R69" t="n">
         <v>7431868</v>
@@ -7705,26 +7705,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126915556</v>
+        <v>126915007</v>
       </c>
       <c r="B70" t="n">
-        <v>57817</v>
+        <v>79632</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7732,31 +7728,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>835394</v>
+        <v>835444</v>
       </c>
       <c r="R70" t="n">
         <v>7431868</v>
@@ -7806,15 +7802,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8513,10 +8513,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126915011</v>
+        <v>126894633</v>
       </c>
       <c r="B78" t="n">
-        <v>91276</v>
+        <v>78773</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8524,21 +8524,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>112</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>835374</v>
+        <v>835411</v>
       </c>
       <c r="R78" t="n">
-        <v>7432212</v>
+        <v>7431972</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8598,12 +8598,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8715,10 +8715,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126894633</v>
+        <v>126915011</v>
       </c>
       <c r="B80" t="n">
-        <v>78773</v>
+        <v>91276</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>112</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>835411</v>
+        <v>835374</v>
       </c>
       <c r="R80" t="n">
-        <v>7431972</v>
+        <v>7432212</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8800,12 +8800,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126893073</v>
+        <v>126893107</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>78685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,6 +1078,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1100,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126893107</v>
+        <v>126893073</v>
       </c>
       <c r="B6" t="n">
-        <v>78681</v>
+        <v>79636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,7 +1180,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1202,32 +1202,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126896461</v>
+        <v>126892873</v>
       </c>
       <c r="B7" t="n">
-        <v>78773</v>
+        <v>97331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>835447</v>
+        <v>835237</v>
       </c>
       <c r="R7" t="n">
-        <v>7431922</v>
+        <v>7431832</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,19 +1270,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,12 +1287,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1313,32 +1303,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126892873</v>
+        <v>126896461</v>
       </c>
       <c r="B8" t="n">
-        <v>97327</v>
+        <v>78777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>835237</v>
+        <v>835447</v>
       </c>
       <c r="R8" t="n">
-        <v>7431832</v>
+        <v>7431922</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,9 +1371,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,12 +1398,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,7 +1417,7 @@
         <v>126893109</v>
       </c>
       <c r="B9" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>126896034</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,32 +1616,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126896048</v>
+        <v>126894504</v>
       </c>
       <c r="B11" t="n">
-        <v>91587</v>
+        <v>92620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>835326</v>
+        <v>835249</v>
       </c>
       <c r="R11" t="n">
-        <v>7431862</v>
+        <v>7431964</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,12 +1701,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1717,32 +1717,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126894504</v>
+        <v>126896048</v>
       </c>
       <c r="B12" t="n">
-        <v>92616</v>
+        <v>91591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>835249</v>
+        <v>835326</v>
       </c>
       <c r="R12" t="n">
-        <v>7431964</v>
+        <v>7431862</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,12 +1802,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1821,7 +1821,7 @@
         <v>126892879</v>
       </c>
       <c r="B13" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,45 +1919,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126895046</v>
+        <v>126893108</v>
       </c>
       <c r="B14" t="n">
-        <v>92616</v>
+        <v>78685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>835398</v>
+        <v>835380</v>
       </c>
       <c r="R14" t="n">
-        <v>7431830</v>
+        <v>7431824</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,12 +2004,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2020,45 +2020,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126893108</v>
+        <v>126895046</v>
       </c>
       <c r="B15" t="n">
-        <v>78681</v>
+        <v>92620</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>835380</v>
+        <v>835398</v>
       </c>
       <c r="R15" t="n">
-        <v>7431824</v>
+        <v>7431830</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,12 +2105,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2121,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126896456</v>
+        <v>126891788</v>
       </c>
       <c r="B16" t="n">
-        <v>79632</v>
+        <v>78685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,21 +2132,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>835435</v>
+        <v>835310</v>
       </c>
       <c r="R16" t="n">
-        <v>7431927</v>
+        <v>7431905</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,19 +2189,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2216,12 +2206,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2232,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126891788</v>
+        <v>126896456</v>
       </c>
       <c r="B17" t="n">
-        <v>78681</v>
+        <v>79636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2243,21 +2233,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2267,10 +2257,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>835310</v>
+        <v>835435</v>
       </c>
       <c r="R17" t="n">
-        <v>7431905</v>
+        <v>7431927</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,9 +2290,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2317,12 +2317,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2336,7 +2336,7 @@
         <v>126893087</v>
       </c>
       <c r="B18" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>126891745</v>
       </c>
       <c r="B19" t="n">
-        <v>91276</v>
+        <v>91280</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126896208</v>
+        <v>126896010</v>
       </c>
       <c r="B20" t="n">
-        <v>97327</v>
+        <v>56596</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>208255</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>835253</v>
+        <v>835133</v>
       </c>
       <c r="R20" t="n">
-        <v>7431988</v>
+        <v>7432014</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2603,19 +2603,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2630,12 +2620,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2646,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126896010</v>
+        <v>126896208</v>
       </c>
       <c r="B21" t="n">
-        <v>56592</v>
+        <v>97331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2657,21 +2647,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208255</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>835133</v>
+        <v>835253</v>
       </c>
       <c r="R21" t="n">
-        <v>7432014</v>
+        <v>7431988</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2714,9 +2704,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2731,12 +2731,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2747,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126896462</v>
+        <v>126891211</v>
       </c>
       <c r="B22" t="n">
-        <v>78772</v>
+        <v>91280</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2758,21 +2758,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>112</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>835438</v>
+        <v>835367</v>
       </c>
       <c r="R22" t="n">
-        <v>7431930</v>
+        <v>7432211</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,19 +2815,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2842,12 +2832,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2861,7 +2851,7 @@
         <v>126891737</v>
       </c>
       <c r="B23" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891211</v>
+        <v>126896462</v>
       </c>
       <c r="B24" t="n">
-        <v>91276</v>
+        <v>78776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,21 +2960,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>112</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>835367</v>
+        <v>835438</v>
       </c>
       <c r="R24" t="n">
-        <v>7432211</v>
+        <v>7431930</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3027,9 +3017,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3044,12 +3044,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3060,32 +3060,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126896052</v>
+        <v>126896216</v>
       </c>
       <c r="B25" t="n">
-        <v>92616</v>
+        <v>57821</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>835305</v>
+        <v>835232</v>
       </c>
       <c r="R25" t="n">
-        <v>7431987</v>
+        <v>7431857</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,9 +3128,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3145,12 +3155,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3161,45 +3171,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126895047</v>
+        <v>126896172</v>
       </c>
       <c r="B26" t="n">
-        <v>92616</v>
+        <v>91591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>835325</v>
+        <v>835412</v>
       </c>
       <c r="R26" t="n">
-        <v>7432027</v>
+        <v>7431868</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3246,26 +3256,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126896216</v>
+        <v>126895020</v>
       </c>
       <c r="B27" t="n">
-        <v>57817</v>
+        <v>91280</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3273,34 +3279,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>112</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>835232</v>
+        <v>835302</v>
       </c>
       <c r="R27" t="n">
-        <v>7431857</v>
+        <v>7431967</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3330,19 +3336,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3357,12 +3353,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3373,45 +3369,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126895020</v>
+        <v>126896052</v>
       </c>
       <c r="B28" t="n">
-        <v>91276</v>
+        <v>92620</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>835302</v>
+        <v>835305</v>
       </c>
       <c r="R28" t="n">
-        <v>7431967</v>
+        <v>7431987</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3458,12 +3454,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3474,45 +3470,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126896172</v>
+        <v>126895047</v>
       </c>
       <c r="B29" t="n">
-        <v>91587</v>
+        <v>92620</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>835412</v>
+        <v>835325</v>
       </c>
       <c r="R29" t="n">
-        <v>7431868</v>
+        <v>7432027</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3559,57 +3555,61 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126895037</v>
+        <v>126894482</v>
       </c>
       <c r="B30" t="n">
-        <v>91487</v>
+        <v>97331</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>835296</v>
+        <v>835253</v>
       </c>
       <c r="R30" t="n">
-        <v>7431963</v>
+        <v>7432159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3656,12 +3656,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3672,10 +3672,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126893081</v>
+        <v>126895037</v>
       </c>
       <c r="B31" t="n">
-        <v>92620</v>
+        <v>91491</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3683,34 +3683,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>835404</v>
+        <v>835296</v>
       </c>
       <c r="R31" t="n">
-        <v>7432008</v>
+        <v>7431963</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3757,12 +3757,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3773,32 +3773,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126894482</v>
+        <v>126893081</v>
       </c>
       <c r="B32" t="n">
-        <v>97327</v>
+        <v>92624</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>4365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>835253</v>
+        <v>835404</v>
       </c>
       <c r="R32" t="n">
-        <v>7432159</v>
+        <v>7432008</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3858,12 +3858,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3874,10 +3874,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126896220</v>
+        <v>126891743</v>
       </c>
       <c r="B33" t="n">
-        <v>82855</v>
+        <v>91350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3885,21 +3885,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>835166</v>
+        <v>835324</v>
       </c>
       <c r="R33" t="n">
-        <v>7431954</v>
+        <v>7431890</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,19 +3942,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3969,12 +3959,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3985,10 +3975,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126891741</v>
+        <v>126896220</v>
       </c>
       <c r="B34" t="n">
-        <v>57657</v>
+        <v>82859</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3996,21 +3986,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4020,10 +4010,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>835254</v>
+        <v>835166</v>
       </c>
       <c r="R34" t="n">
-        <v>7432142</v>
+        <v>7431954</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,9 +4043,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4070,12 +4070,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4086,10 +4086,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126891743</v>
+        <v>126891741</v>
       </c>
       <c r="B35" t="n">
-        <v>91346</v>
+        <v>57661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4097,21 +4097,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>835324</v>
+        <v>835254</v>
       </c>
       <c r="R35" t="n">
-        <v>7431890</v>
+        <v>7432142</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4190,7 +4190,7 @@
         <v>126896454</v>
       </c>
       <c r="B36" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>126893092</v>
       </c>
       <c r="B37" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4399,10 +4399,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126891761</v>
+        <v>126895021</v>
       </c>
       <c r="B38" t="n">
-        <v>105478</v>
+        <v>97331</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4410,34 +4410,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>835274</v>
+        <v>835445</v>
       </c>
       <c r="R38" t="n">
-        <v>7431953</v>
+        <v>7432004</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4484,12 +4484,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4500,10 +4500,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126895021</v>
+        <v>126891761</v>
       </c>
       <c r="B39" t="n">
-        <v>97327</v>
+        <v>105484</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4511,34 +4511,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>835445</v>
+        <v>835274</v>
       </c>
       <c r="R39" t="n">
-        <v>7432004</v>
+        <v>7431953</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4585,12 +4585,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4604,7 +4604,7 @@
         <v>126896476</v>
       </c>
       <c r="B40" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>126896015</v>
       </c>
       <c r="B41" t="n">
-        <v>79038</v>
+        <v>79042</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>126896012</v>
       </c>
       <c r="B42" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4914,10 +4914,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126892874</v>
+        <v>126896207</v>
       </c>
       <c r="B43" t="n">
-        <v>75138</v>
+        <v>79636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4925,21 +4925,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>835180</v>
+        <v>835216</v>
       </c>
       <c r="R43" t="n">
-        <v>7431962</v>
+        <v>7432256</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4982,9 +4982,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4999,12 +5009,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5018,7 +5028,7 @@
         <v>126896215</v>
       </c>
       <c r="B44" t="n">
-        <v>95300</v>
+        <v>95304</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5126,10 +5136,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126896207</v>
+        <v>126892874</v>
       </c>
       <c r="B45" t="n">
-        <v>79632</v>
+        <v>75142</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5137,21 +5147,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5161,10 +5171,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>835216</v>
+        <v>835180</v>
       </c>
       <c r="R45" t="n">
-        <v>7432256</v>
+        <v>7431962</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5194,19 +5204,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5221,12 +5221,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5240,7 +5240,7 @@
         <v>126896001</v>
       </c>
       <c r="B46" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126896013</v>
+        <v>126891762</v>
       </c>
       <c r="B47" t="n">
-        <v>97327</v>
+        <v>105484</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>835330</v>
+        <v>835361</v>
       </c>
       <c r="R47" t="n">
-        <v>7431947</v>
+        <v>7431869</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5423,12 +5423,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5439,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126891762</v>
+        <v>126896013</v>
       </c>
       <c r="B48" t="n">
-        <v>105478</v>
+        <v>97331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5450,21 +5450,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>835361</v>
+        <v>835330</v>
       </c>
       <c r="R48" t="n">
-        <v>7431869</v>
+        <v>7431947</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,12 +5524,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5540,32 +5540,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126896453</v>
+        <v>126896459</v>
       </c>
       <c r="B49" t="n">
-        <v>79632</v>
+        <v>97331</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>835315</v>
+        <v>835386</v>
       </c>
       <c r="R49" t="n">
-        <v>7432233</v>
+        <v>7432177</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5651,32 +5651,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126896459</v>
+        <v>126896453</v>
       </c>
       <c r="B50" t="n">
-        <v>97327</v>
+        <v>79636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5686,10 +5686,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>835386</v>
+        <v>835315</v>
       </c>
       <c r="R50" t="n">
-        <v>7432177</v>
+        <v>7432233</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5762,10 +5762,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126893090</v>
+        <v>126896046</v>
       </c>
       <c r="B51" t="n">
-        <v>92608</v>
+        <v>82859</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5773,21 +5773,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4361</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5797,10 +5797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>835354</v>
+        <v>835241</v>
       </c>
       <c r="R51" t="n">
-        <v>7431995</v>
+        <v>7432287</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5847,12 +5847,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5863,45 +5863,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126896455</v>
+        <v>126895028</v>
       </c>
       <c r="B52" t="n">
-        <v>79632</v>
+        <v>91258</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>2013</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>835445</v>
+        <v>835423</v>
       </c>
       <c r="R52" t="n">
-        <v>7431926</v>
+        <v>7431886</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5931,19 +5931,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5958,12 +5948,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5974,32 +5964,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126893083</v>
+        <v>126893090</v>
       </c>
       <c r="B53" t="n">
-        <v>97321</v>
+        <v>92612</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6009,10 +5999,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>835458</v>
+        <v>835354</v>
       </c>
       <c r="R53" t="n">
-        <v>7431881</v>
+        <v>7431995</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6075,10 +6065,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126896046</v>
+        <v>126896455</v>
       </c>
       <c r="B54" t="n">
-        <v>82855</v>
+        <v>79636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6086,21 +6076,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6110,10 +6100,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>835241</v>
+        <v>835445</v>
       </c>
       <c r="R54" t="n">
-        <v>7432287</v>
+        <v>7431926</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6143,9 +6133,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6160,12 +6160,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6176,45 +6176,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126895028</v>
+        <v>126893083</v>
       </c>
       <c r="B55" t="n">
-        <v>91254</v>
+        <v>97325</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2013</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>835423</v>
+        <v>835458</v>
       </c>
       <c r="R55" t="n">
-        <v>7431886</v>
+        <v>7431881</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6261,12 +6261,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6277,10 +6277,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126891218</v>
+        <v>126891747</v>
       </c>
       <c r="B56" t="n">
-        <v>92616</v>
+        <v>80025</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6288,21 +6288,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>835411</v>
+        <v>835247</v>
       </c>
       <c r="R56" t="n">
-        <v>7432011</v>
+        <v>7432156</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6362,12 +6362,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6381,7 +6381,7 @@
         <v>126895019</v>
       </c>
       <c r="B57" t="n">
-        <v>91276</v>
+        <v>91280</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6479,10 +6479,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126891747</v>
+        <v>126891218</v>
       </c>
       <c r="B58" t="n">
-        <v>80021</v>
+        <v>92620</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6490,21 +6490,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>835247</v>
+        <v>835411</v>
       </c>
       <c r="R58" t="n">
-        <v>7432156</v>
+        <v>7432011</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6564,12 +6564,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6583,7 +6583,7 @@
         <v>126892867</v>
       </c>
       <c r="B59" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6686,45 +6686,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126895027</v>
+        <v>126896035</v>
       </c>
       <c r="B60" t="n">
-        <v>58027</v>
+        <v>98447</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>835398</v>
+        <v>835290</v>
       </c>
       <c r="R60" t="n">
-        <v>7431822</v>
+        <v>7432175</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6771,12 +6771,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6790,7 +6790,7 @@
         <v>126892870</v>
       </c>
       <c r="B61" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6888,45 +6888,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126896035</v>
+        <v>126895027</v>
       </c>
       <c r="B62" t="n">
-        <v>98443</v>
+        <v>58031</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>835290</v>
+        <v>835398</v>
       </c>
       <c r="R62" t="n">
-        <v>7432175</v>
+        <v>7431822</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6973,12 +6973,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6989,32 +6989,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126896458</v>
+        <v>126894490</v>
       </c>
       <c r="B63" t="n">
-        <v>91276</v>
+        <v>91491</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>112</v>
+        <v>1503</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>835425</v>
+        <v>835300</v>
       </c>
       <c r="R63" t="n">
-        <v>7431979</v>
+        <v>7431907</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7057,19 +7057,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7084,12 +7074,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7103,7 +7093,7 @@
         <v>126896213</v>
       </c>
       <c r="B64" t="n">
-        <v>100598</v>
+        <v>100602</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7211,32 +7201,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126894490</v>
+        <v>126896051</v>
       </c>
       <c r="B65" t="n">
-        <v>91487</v>
+        <v>98364</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1503</v>
+        <v>219790</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7246,10 +7236,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>835300</v>
+        <v>835330</v>
       </c>
       <c r="R65" t="n">
-        <v>7431907</v>
+        <v>7432131</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7296,12 +7286,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7312,32 +7302,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126892868</v>
+        <v>126896458</v>
       </c>
       <c r="B66" t="n">
-        <v>56849</v>
+        <v>91280</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>112</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7347,10 +7337,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>835234</v>
+        <v>835425</v>
       </c>
       <c r="R66" t="n">
-        <v>7431879</v>
+        <v>7431979</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,14 +7370,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7402,12 +7397,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7418,32 +7413,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126894487</v>
+        <v>126892868</v>
       </c>
       <c r="B67" t="n">
-        <v>56840</v>
+        <v>56853</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7453,10 +7448,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>835105</v>
+        <v>835234</v>
       </c>
       <c r="R67" t="n">
-        <v>7432062</v>
+        <v>7431879</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7491,6 +7486,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7503,12 +7503,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7519,32 +7519,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126896051</v>
+        <v>126894487</v>
       </c>
       <c r="B68" t="n">
-        <v>98360</v>
+        <v>56844</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>835330</v>
+        <v>835105</v>
       </c>
       <c r="R68" t="n">
-        <v>7432131</v>
+        <v>7432062</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7604,12 +7604,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7623,7 +7623,7 @@
         <v>126915556</v>
       </c>
       <c r="B69" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>126915007</v>
       </c>
       <c r="B70" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>126894627</v>
       </c>
       <c r="B71" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>126915557</v>
       </c>
       <c r="B72" t="n">
-        <v>92628</v>
+        <v>92632</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126894632</v>
+        <v>126915019</v>
       </c>
       <c r="B73" t="n">
-        <v>92809</v>
+        <v>92813</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>835406</v>
+        <v>835275</v>
       </c>
       <c r="R73" t="n">
-        <v>7431965</v>
+        <v>7432030</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8101,12 +8101,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8117,45 +8117,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126915019</v>
+        <v>126915568</v>
       </c>
       <c r="B74" t="n">
-        <v>92809</v>
+        <v>92620</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>835275</v>
+        <v>835341</v>
       </c>
       <c r="R74" t="n">
-        <v>7432030</v>
+        <v>7432052</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8202,61 +8202,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126915568</v>
+        <v>126894632</v>
       </c>
       <c r="B75" t="n">
-        <v>92616</v>
+        <v>92813</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>835341</v>
+        <v>835406</v>
       </c>
       <c r="R75" t="n">
-        <v>7432052</v>
+        <v>7431965</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8303,22 +8299,26 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>126915562</v>
       </c>
       <c r="B76" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>126915015</v>
       </c>
       <c r="B77" t="n">
-        <v>79038</v>
+        <v>79042</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8513,10 +8513,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126894633</v>
+        <v>126915032</v>
       </c>
       <c r="B78" t="n">
-        <v>78773</v>
+        <v>78424</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8524,21 +8524,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>835411</v>
+        <v>835212</v>
       </c>
       <c r="R78" t="n">
-        <v>7431972</v>
+        <v>7432119</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8598,12 +8598,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8614,10 +8614,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126915032</v>
+        <v>126894633</v>
       </c>
       <c r="B79" t="n">
-        <v>78420</v>
+        <v>78777</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8625,21 +8625,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>835212</v>
+        <v>835411</v>
       </c>
       <c r="R79" t="n">
-        <v>7432119</v>
+        <v>7431972</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8699,12 +8699,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8718,7 +8718,7 @@
         <v>126915011</v>
       </c>
       <c r="B80" t="n">
-        <v>91276</v>
+        <v>91280</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>126915016</v>
       </c>
       <c r="B81" t="n">
-        <v>79038</v>
+        <v>79042</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>126894643</v>
       </c>
       <c r="B82" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>126916087</v>
       </c>
       <c r="B83" t="n">
-        <v>92642</v>
+        <v>92646</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>126915017</v>
       </c>
       <c r="B84" t="n">
-        <v>79038</v>
+        <v>79042</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>126927927</v>
       </c>
       <c r="B85" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>126927910</v>
       </c>
       <c r="B86" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>126891792</v>
       </c>
       <c r="B87" t="n">
-        <v>79984</v>
+        <v>79988</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>126927931</v>
       </c>
       <c r="B88" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>126943155</v>
       </c>
       <c r="B89" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>126943164</v>
       </c>
       <c r="B90" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9854,32 +9854,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126943156</v>
+        <v>126943157</v>
       </c>
       <c r="B91" t="n">
-        <v>92616</v>
+        <v>77996</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>835445</v>
+        <v>835394</v>
       </c>
       <c r="R91" t="n">
-        <v>7431908</v>
+        <v>7431928</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9955,32 +9955,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126943157</v>
+        <v>126943156</v>
       </c>
       <c r="B92" t="n">
-        <v>77992</v>
+        <v>92620</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>835394</v>
+        <v>835445</v>
       </c>
       <c r="R92" t="n">
-        <v>7431928</v>
+        <v>7431908</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10059,7 +10059,7 @@
         <v>126943160</v>
       </c>
       <c r="B93" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>126943150</v>
       </c>
       <c r="B94" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>126943163</v>
       </c>
       <c r="B95" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>126943159</v>
       </c>
       <c r="B96" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>126943161</v>
       </c>
       <c r="B97" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10571,32 +10571,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126943153</v>
+        <v>126943151</v>
       </c>
       <c r="B98" t="n">
-        <v>98443</v>
+        <v>92620</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>835440</v>
+        <v>835382</v>
       </c>
       <c r="R98" t="n">
-        <v>7431856</v>
+        <v>7432189</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10672,32 +10672,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126943151</v>
+        <v>126943153</v>
       </c>
       <c r="B99" t="n">
-        <v>92616</v>
+        <v>98447</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>835382</v>
+        <v>835440</v>
       </c>
       <c r="R99" t="n">
-        <v>7432189</v>
+        <v>7431856</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10773,10 +10773,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127414787</v>
+        <v>127414788</v>
       </c>
       <c r="B100" t="n">
-        <v>92610</v>
+        <v>92612</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10784,21 +10784,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>835307</v>
+        <v>835310</v>
       </c>
       <c r="R100" t="n">
-        <v>7432078</v>
+        <v>7432075</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10879,10 +10879,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127414788</v>
+        <v>127414787</v>
       </c>
       <c r="B101" t="n">
-        <v>92608</v>
+        <v>92614</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10890,21 +10890,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10918,10 +10918,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>835310</v>
+        <v>835307</v>
       </c>
       <c r="R101" t="n">
-        <v>7432075</v>
+        <v>7432078</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -1616,32 +1616,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126894504</v>
+        <v>126896048</v>
       </c>
       <c r="B11" t="n">
-        <v>92620</v>
+        <v>91591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>835249</v>
+        <v>835326</v>
       </c>
       <c r="R11" t="n">
-        <v>7431964</v>
+        <v>7431862</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,12 +1701,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1717,32 +1717,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126896048</v>
+        <v>126894504</v>
       </c>
       <c r="B12" t="n">
-        <v>91591</v>
+        <v>92620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>835326</v>
+        <v>835249</v>
       </c>
       <c r="R12" t="n">
-        <v>7431862</v>
+        <v>7431964</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,12 +1802,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2121,32 +2121,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126891788</v>
+        <v>126893087</v>
       </c>
       <c r="B16" t="n">
-        <v>78685</v>
+        <v>97331</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>835310</v>
+        <v>835357</v>
       </c>
       <c r="R16" t="n">
-        <v>7431905</v>
+        <v>7432179</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,12 +2206,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2222,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126896456</v>
+        <v>126891788</v>
       </c>
       <c r="B17" t="n">
-        <v>79636</v>
+        <v>78685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>835435</v>
+        <v>835310</v>
       </c>
       <c r="R17" t="n">
-        <v>7431927</v>
+        <v>7431905</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,19 +2290,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2317,12 +2307,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2333,32 +2323,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126893087</v>
+        <v>126896456</v>
       </c>
       <c r="B18" t="n">
-        <v>97331</v>
+        <v>79636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2368,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>835357</v>
+        <v>835435</v>
       </c>
       <c r="R18" t="n">
-        <v>7432179</v>
+        <v>7431927</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2401,9 +2391,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,12 +2418,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2747,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126891211</v>
+        <v>126896462</v>
       </c>
       <c r="B22" t="n">
-        <v>91280</v>
+        <v>78776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2758,21 +2758,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>835367</v>
+        <v>835438</v>
       </c>
       <c r="R22" t="n">
-        <v>7432211</v>
+        <v>7431930</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,9 +2815,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2832,12 +2842,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2949,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126896462</v>
+        <v>126891211</v>
       </c>
       <c r="B24" t="n">
-        <v>78776</v>
+        <v>91280</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2960,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>112</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>835438</v>
+        <v>835367</v>
       </c>
       <c r="R24" t="n">
-        <v>7431930</v>
+        <v>7432211</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3017,19 +3027,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3044,12 +3044,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3060,10 +3060,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126896216</v>
+        <v>126895020</v>
       </c>
       <c r="B25" t="n">
-        <v>57821</v>
+        <v>91280</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,34 +3071,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>112</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>835232</v>
+        <v>835302</v>
       </c>
       <c r="R25" t="n">
-        <v>7431857</v>
+        <v>7431967</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,19 +3128,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3155,12 +3145,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3268,45 +3258,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126895020</v>
+        <v>126896052</v>
       </c>
       <c r="B27" t="n">
-        <v>91280</v>
+        <v>92620</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>835302</v>
+        <v>835305</v>
       </c>
       <c r="R27" t="n">
-        <v>7431967</v>
+        <v>7431987</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3353,12 +3343,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3369,7 +3359,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126896052</v>
+        <v>126895047</v>
       </c>
       <c r="B28" t="n">
         <v>92620</v>
@@ -3400,14 +3390,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>835305</v>
+        <v>835325</v>
       </c>
       <c r="R28" t="n">
-        <v>7431987</v>
+        <v>7432027</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,12 +3444,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3470,45 +3460,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126895047</v>
+        <v>126896216</v>
       </c>
       <c r="B29" t="n">
-        <v>92620</v>
+        <v>57821</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>835325</v>
+        <v>835232</v>
       </c>
       <c r="R29" t="n">
-        <v>7432027</v>
+        <v>7431857</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,9 +3528,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3555,12 +3555,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3571,45 +3571,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126894482</v>
+        <v>126895037</v>
       </c>
       <c r="B30" t="n">
-        <v>97331</v>
+        <v>91491</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>835253</v>
+        <v>835296</v>
       </c>
       <c r="R30" t="n">
-        <v>7432159</v>
+        <v>7431963</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3656,12 +3656,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3672,10 +3672,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126895037</v>
+        <v>126893081</v>
       </c>
       <c r="B31" t="n">
-        <v>91491</v>
+        <v>92624</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3683,34 +3683,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>835296</v>
+        <v>835404</v>
       </c>
       <c r="R31" t="n">
-        <v>7431963</v>
+        <v>7432008</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3757,12 +3757,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3773,32 +3773,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126893081</v>
+        <v>126894482</v>
       </c>
       <c r="B32" t="n">
-        <v>92624</v>
+        <v>97331</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4365</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>835404</v>
+        <v>835253</v>
       </c>
       <c r="R32" t="n">
-        <v>7432008</v>
+        <v>7432159</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3858,12 +3858,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3874,10 +3874,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126891743</v>
+        <v>126896220</v>
       </c>
       <c r="B33" t="n">
-        <v>91350</v>
+        <v>82859</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3885,21 +3885,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>835324</v>
+        <v>835166</v>
       </c>
       <c r="R33" t="n">
-        <v>7431890</v>
+        <v>7431954</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,9 +3942,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3959,12 +3969,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3975,10 +3985,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126896220</v>
+        <v>126891743</v>
       </c>
       <c r="B34" t="n">
-        <v>82859</v>
+        <v>91350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3986,21 +3996,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4010,10 +4020,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>835166</v>
+        <v>835324</v>
       </c>
       <c r="R34" t="n">
-        <v>7431954</v>
+        <v>7431890</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,19 +4053,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4070,12 +4070,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4086,10 +4086,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126891741</v>
+        <v>126896454</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4097,21 +4097,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>835254</v>
+        <v>835391</v>
       </c>
       <c r="R35" t="n">
-        <v>7432142</v>
+        <v>7431880</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4154,9 +4154,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4171,12 +4181,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4187,10 +4197,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126896454</v>
+        <v>126891741</v>
       </c>
       <c r="B36" t="n">
-        <v>79636</v>
+        <v>57661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4198,21 +4208,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4222,10 +4232,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>835391</v>
+        <v>835254</v>
       </c>
       <c r="R36" t="n">
-        <v>7431880</v>
+        <v>7432142</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,19 +4265,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4282,12 +4282,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4399,10 +4399,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126895021</v>
+        <v>126891761</v>
       </c>
       <c r="B38" t="n">
-        <v>97331</v>
+        <v>105484</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4410,34 +4410,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>835445</v>
+        <v>835274</v>
       </c>
       <c r="R38" t="n">
-        <v>7432004</v>
+        <v>7431953</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4484,12 +4484,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4500,10 +4500,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126891761</v>
+        <v>126895021</v>
       </c>
       <c r="B39" t="n">
-        <v>105484</v>
+        <v>97331</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4511,34 +4511,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>835274</v>
+        <v>835445</v>
       </c>
       <c r="R39" t="n">
-        <v>7431953</v>
+        <v>7432004</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4585,12 +4585,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4601,32 +4601,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126896476</v>
+        <v>126896012</v>
       </c>
       <c r="B40" t="n">
-        <v>78685</v>
+        <v>97325</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>835392</v>
+        <v>835330</v>
       </c>
       <c r="R40" t="n">
-        <v>7431887</v>
+        <v>7432136</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4669,19 +4669,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4696,12 +4686,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4712,32 +4702,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126896015</v>
+        <v>126896476</v>
       </c>
       <c r="B41" t="n">
-        <v>79042</v>
+        <v>78685</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4747,10 +4737,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>835346</v>
+        <v>835392</v>
       </c>
       <c r="R41" t="n">
-        <v>7431909</v>
+        <v>7431887</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,9 +4770,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4797,12 +4797,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4813,10 +4813,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126896012</v>
+        <v>126896015</v>
       </c>
       <c r="B42" t="n">
-        <v>97325</v>
+        <v>79042</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4824,21 +4824,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>835330</v>
+        <v>835346</v>
       </c>
       <c r="R42" t="n">
-        <v>7432136</v>
+        <v>7431909</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4914,32 +4914,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126896207</v>
+        <v>126896215</v>
       </c>
       <c r="B43" t="n">
-        <v>79636</v>
+        <v>95304</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>2387</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>835216</v>
+        <v>835224</v>
       </c>
       <c r="R43" t="n">
-        <v>7432256</v>
+        <v>7431834</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5025,32 +5025,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126896215</v>
+        <v>126896207</v>
       </c>
       <c r="B44" t="n">
-        <v>95304</v>
+        <v>79636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2387</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>835224</v>
+        <v>835216</v>
       </c>
       <c r="R44" t="n">
-        <v>7431834</v>
+        <v>7432256</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5540,32 +5540,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126896459</v>
+        <v>126896453</v>
       </c>
       <c r="B49" t="n">
-        <v>97331</v>
+        <v>79636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>835386</v>
+        <v>835315</v>
       </c>
       <c r="R49" t="n">
-        <v>7432177</v>
+        <v>7432233</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5651,32 +5651,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126896453</v>
+        <v>126896459</v>
       </c>
       <c r="B50" t="n">
-        <v>79636</v>
+        <v>97331</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5686,10 +5686,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>835315</v>
+        <v>835386</v>
       </c>
       <c r="R50" t="n">
-        <v>7432233</v>
+        <v>7432177</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5762,45 +5762,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126896046</v>
+        <v>126895028</v>
       </c>
       <c r="B51" t="n">
-        <v>82859</v>
+        <v>91258</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>2013</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>835241</v>
+        <v>835423</v>
       </c>
       <c r="R51" t="n">
-        <v>7432287</v>
+        <v>7431886</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5847,12 +5847,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5863,45 +5863,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126895028</v>
+        <v>126896046</v>
       </c>
       <c r="B52" t="n">
-        <v>91258</v>
+        <v>82859</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2013</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>835423</v>
+        <v>835241</v>
       </c>
       <c r="R52" t="n">
-        <v>7431886</v>
+        <v>7432287</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5948,12 +5948,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5964,10 +5964,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126893090</v>
+        <v>126896455</v>
       </c>
       <c r="B53" t="n">
-        <v>92612</v>
+        <v>79636</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5975,21 +5975,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5999,10 +5999,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>835354</v>
+        <v>835445</v>
       </c>
       <c r="R53" t="n">
-        <v>7431995</v>
+        <v>7431926</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6032,9 +6032,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6049,12 +6059,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6065,32 +6075,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126896455</v>
+        <v>126893083</v>
       </c>
       <c r="B54" t="n">
-        <v>79636</v>
+        <v>97325</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6100,10 +6110,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>835445</v>
+        <v>835458</v>
       </c>
       <c r="R54" t="n">
-        <v>7431926</v>
+        <v>7431881</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6133,19 +6143,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6160,12 +6160,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6176,32 +6176,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893083</v>
+        <v>126893090</v>
       </c>
       <c r="B55" t="n">
-        <v>97325</v>
+        <v>92612</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>835458</v>
+        <v>835354</v>
       </c>
       <c r="R55" t="n">
-        <v>7431881</v>
+        <v>7431995</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6277,45 +6277,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126891747</v>
+        <v>126895019</v>
       </c>
       <c r="B56" t="n">
-        <v>80025</v>
+        <v>91280</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>112</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>835247</v>
+        <v>835295</v>
       </c>
       <c r="R56" t="n">
-        <v>7432156</v>
+        <v>7431936</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6362,12 +6362,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6378,45 +6378,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126895019</v>
+        <v>126891218</v>
       </c>
       <c r="B57" t="n">
-        <v>91280</v>
+        <v>92620</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>835295</v>
+        <v>835411</v>
       </c>
       <c r="R57" t="n">
-        <v>7431936</v>
+        <v>7432011</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6463,12 +6463,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6479,10 +6479,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126891218</v>
+        <v>126891747</v>
       </c>
       <c r="B58" t="n">
-        <v>92620</v>
+        <v>80025</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6490,21 +6490,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>835411</v>
+        <v>835247</v>
       </c>
       <c r="R58" t="n">
-        <v>7432011</v>
+        <v>7432156</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6564,12 +6564,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6686,45 +6686,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126896035</v>
+        <v>126895027</v>
       </c>
       <c r="B60" t="n">
-        <v>98447</v>
+        <v>58031</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>835290</v>
+        <v>835398</v>
       </c>
       <c r="R60" t="n">
-        <v>7432175</v>
+        <v>7431822</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6771,12 +6771,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6888,45 +6888,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126895027</v>
+        <v>126896035</v>
       </c>
       <c r="B62" t="n">
-        <v>58031</v>
+        <v>98447</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>835398</v>
+        <v>835290</v>
       </c>
       <c r="R62" t="n">
-        <v>7431822</v>
+        <v>7432175</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6973,12 +6973,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7201,10 +7201,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126896051</v>
+        <v>126892868</v>
       </c>
       <c r="B65" t="n">
-        <v>98364</v>
+        <v>56853</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7212,21 +7212,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7236,10 +7236,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>835330</v>
+        <v>835234</v>
       </c>
       <c r="R65" t="n">
-        <v>7432131</v>
+        <v>7431879</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7274,6 +7274,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7286,12 +7291,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7302,10 +7307,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126896458</v>
+        <v>126894487</v>
       </c>
       <c r="B66" t="n">
-        <v>91280</v>
+        <v>56844</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7313,21 +7318,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>112</v>
+        <v>102612</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7337,10 +7342,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>835425</v>
+        <v>835105</v>
       </c>
       <c r="R66" t="n">
-        <v>7431979</v>
+        <v>7432062</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7370,19 +7375,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7397,12 +7392,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7413,10 +7408,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126892868</v>
+        <v>126896051</v>
       </c>
       <c r="B67" t="n">
-        <v>56853</v>
+        <v>98364</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7424,21 +7419,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7448,10 +7443,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>835234</v>
+        <v>835330</v>
       </c>
       <c r="R67" t="n">
-        <v>7431879</v>
+        <v>7432131</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7486,11 +7481,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7503,12 +7493,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7519,10 +7509,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126894487</v>
+        <v>126896458</v>
       </c>
       <c r="B68" t="n">
-        <v>56844</v>
+        <v>91280</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7530,21 +7520,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102612</v>
+        <v>112</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7554,10 +7544,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>835105</v>
+        <v>835425</v>
       </c>
       <c r="R68" t="n">
-        <v>7432062</v>
+        <v>7431979</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7587,9 +7577,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7604,12 +7604,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7620,10 +7620,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126915556</v>
+        <v>126915007</v>
       </c>
       <c r="B69" t="n">
-        <v>57821</v>
+        <v>79636</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7631,31 +7631,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>835394</v>
+        <v>835444</v>
       </c>
       <c r="R69" t="n">
         <v>7431868</v>
@@ -7705,22 +7705,26 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126915007</v>
+        <v>126915556</v>
       </c>
       <c r="B70" t="n">
-        <v>79636</v>
+        <v>57821</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7728,31 +7732,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>835444</v>
+        <v>835394</v>
       </c>
       <c r="R70" t="n">
         <v>7431868</v>
@@ -7802,19 +7806,15 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8016,7 +8016,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126915019</v>
+        <v>126894632</v>
       </c>
       <c r="B73" t="n">
         <v>92813</v>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>835275</v>
+        <v>835406</v>
       </c>
       <c r="R73" t="n">
-        <v>7432030</v>
+        <v>7431965</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8101,12 +8101,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8117,45 +8117,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126915568</v>
+        <v>126915019</v>
       </c>
       <c r="B74" t="n">
-        <v>92620</v>
+        <v>92813</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>835341</v>
+        <v>835275</v>
       </c>
       <c r="R74" t="n">
-        <v>7432052</v>
+        <v>7432030</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8202,57 +8202,61 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126894632</v>
+        <v>126915568</v>
       </c>
       <c r="B75" t="n">
-        <v>92813</v>
+        <v>92620</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>835406</v>
+        <v>835341</v>
       </c>
       <c r="R75" t="n">
-        <v>7431965</v>
+        <v>7432052</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8299,19 +8303,15 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8513,10 +8513,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126915032</v>
+        <v>126894633</v>
       </c>
       <c r="B78" t="n">
-        <v>78424</v>
+        <v>78777</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8524,21 +8524,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>835212</v>
+        <v>835411</v>
       </c>
       <c r="R78" t="n">
-        <v>7432119</v>
+        <v>7431972</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8598,12 +8598,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8614,10 +8614,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126894633</v>
+        <v>126915032</v>
       </c>
       <c r="B79" t="n">
-        <v>78777</v>
+        <v>78424</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8625,21 +8625,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>835411</v>
+        <v>835212</v>
       </c>
       <c r="R79" t="n">
-        <v>7431972</v>
+        <v>7432119</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8699,12 +8699,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -10773,10 +10773,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127414788</v>
+        <v>127414787</v>
       </c>
       <c r="B100" t="n">
-        <v>92612</v>
+        <v>92614</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10784,21 +10784,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>835310</v>
+        <v>835307</v>
       </c>
       <c r="R100" t="n">
-        <v>7432075</v>
+        <v>7432078</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10879,10 +10879,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127414787</v>
+        <v>127414788</v>
       </c>
       <c r="B101" t="n">
-        <v>92614</v>
+        <v>92612</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10890,21 +10890,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10918,10 +10918,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>835307</v>
+        <v>835310</v>
       </c>
       <c r="R101" t="n">
-        <v>7432078</v>
+        <v>7432075</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -1616,32 +1616,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126896048</v>
+        <v>126894504</v>
       </c>
       <c r="B11" t="n">
-        <v>91591</v>
+        <v>92620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>835326</v>
+        <v>835249</v>
       </c>
       <c r="R11" t="n">
-        <v>7431862</v>
+        <v>7431964</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,12 +1701,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1717,32 +1717,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126894504</v>
+        <v>126896048</v>
       </c>
       <c r="B12" t="n">
-        <v>92620</v>
+        <v>91591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>835249</v>
+        <v>835326</v>
       </c>
       <c r="R12" t="n">
-        <v>7431964</v>
+        <v>7431862</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,12 +1802,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2121,32 +2121,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126893087</v>
+        <v>126891788</v>
       </c>
       <c r="B16" t="n">
-        <v>97331</v>
+        <v>78685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>835357</v>
+        <v>835310</v>
       </c>
       <c r="R16" t="n">
-        <v>7432179</v>
+        <v>7431905</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,12 +2206,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2222,32 +2222,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126891788</v>
+        <v>126893087</v>
       </c>
       <c r="B17" t="n">
-        <v>78685</v>
+        <v>97331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>835310</v>
+        <v>835357</v>
       </c>
       <c r="R17" t="n">
-        <v>7431905</v>
+        <v>7432179</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,12 +2307,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126896010</v>
+        <v>126896208</v>
       </c>
       <c r="B20" t="n">
-        <v>56596</v>
+        <v>97331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208255</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>835133</v>
+        <v>835253</v>
       </c>
       <c r="R20" t="n">
-        <v>7432014</v>
+        <v>7431988</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2603,9 +2603,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2620,12 +2630,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2636,10 +2646,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126896208</v>
+        <v>126896010</v>
       </c>
       <c r="B21" t="n">
-        <v>97331</v>
+        <v>56596</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2647,21 +2657,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>208255</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2671,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>835253</v>
+        <v>835133</v>
       </c>
       <c r="R21" t="n">
-        <v>7431988</v>
+        <v>7432014</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,19 +2714,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2731,12 +2731,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3571,45 +3571,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126895037</v>
+        <v>126894482</v>
       </c>
       <c r="B30" t="n">
-        <v>91491</v>
+        <v>97331</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>835296</v>
+        <v>835253</v>
       </c>
       <c r="R30" t="n">
-        <v>7431963</v>
+        <v>7432159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3656,12 +3656,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3672,10 +3672,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126893081</v>
+        <v>126895037</v>
       </c>
       <c r="B31" t="n">
-        <v>92624</v>
+        <v>91491</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3683,34 +3683,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>835404</v>
+        <v>835296</v>
       </c>
       <c r="R31" t="n">
-        <v>7432008</v>
+        <v>7431963</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3757,12 +3757,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3773,32 +3773,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126894482</v>
+        <v>126893081</v>
       </c>
       <c r="B32" t="n">
-        <v>97331</v>
+        <v>92624</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>4365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>835253</v>
+        <v>835404</v>
       </c>
       <c r="R32" t="n">
-        <v>7432159</v>
+        <v>7432008</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3858,12 +3858,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3874,32 +3874,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126896220</v>
+        <v>126893092</v>
       </c>
       <c r="B33" t="n">
-        <v>82859</v>
+        <v>97331</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>835166</v>
+        <v>835234</v>
       </c>
       <c r="R33" t="n">
-        <v>7431954</v>
+        <v>7432287</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,19 +3942,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3969,12 +3959,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3985,10 +3975,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126891743</v>
+        <v>126896220</v>
       </c>
       <c r="B34" t="n">
-        <v>91350</v>
+        <v>82859</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3996,21 +3986,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4020,10 +4010,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>835324</v>
+        <v>835166</v>
       </c>
       <c r="R34" t="n">
-        <v>7431890</v>
+        <v>7431954</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,9 +4043,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4070,12 +4070,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4086,10 +4086,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126896454</v>
+        <v>126891743</v>
       </c>
       <c r="B35" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4097,21 +4097,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>835391</v>
+        <v>835324</v>
       </c>
       <c r="R35" t="n">
-        <v>7431880</v>
+        <v>7431890</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4154,19 +4154,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4181,12 +4171,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4197,10 +4187,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126891741</v>
+        <v>126896454</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4208,21 +4198,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4232,10 +4222,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>835254</v>
+        <v>835391</v>
       </c>
       <c r="R36" t="n">
-        <v>7432142</v>
+        <v>7431880</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,9 +4255,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4282,12 +4282,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4298,32 +4298,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126893092</v>
+        <v>126891741</v>
       </c>
       <c r="B37" t="n">
-        <v>97331</v>
+        <v>57661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>835234</v>
+        <v>835254</v>
       </c>
       <c r="R37" t="n">
-        <v>7432287</v>
+        <v>7432142</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4383,12 +4383,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -5762,45 +5762,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126895028</v>
+        <v>126893090</v>
       </c>
       <c r="B51" t="n">
-        <v>91258</v>
+        <v>92612</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2013</v>
+        <v>4361</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>835423</v>
+        <v>835354</v>
       </c>
       <c r="R51" t="n">
-        <v>7431886</v>
+        <v>7431995</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5847,12 +5847,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5863,10 +5863,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126896046</v>
+        <v>126896455</v>
       </c>
       <c r="B52" t="n">
-        <v>82859</v>
+        <v>79636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5874,21 +5874,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5898,10 +5898,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>835241</v>
+        <v>835445</v>
       </c>
       <c r="R52" t="n">
-        <v>7432287</v>
+        <v>7431926</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5931,9 +5931,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5948,12 +5958,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5964,32 +5974,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126896455</v>
+        <v>126893083</v>
       </c>
       <c r="B53" t="n">
-        <v>79636</v>
+        <v>97325</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5999,10 +6009,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>835445</v>
+        <v>835458</v>
       </c>
       <c r="R53" t="n">
-        <v>7431926</v>
+        <v>7431881</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6032,19 +6042,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6059,12 +6059,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6075,45 +6075,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126893083</v>
+        <v>126895028</v>
       </c>
       <c r="B54" t="n">
-        <v>97325</v>
+        <v>91258</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>2013</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>835458</v>
+        <v>835423</v>
       </c>
       <c r="R54" t="n">
-        <v>7431881</v>
+        <v>7431886</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6160,12 +6160,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6176,10 +6176,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893090</v>
+        <v>126896046</v>
       </c>
       <c r="B55" t="n">
-        <v>92612</v>
+        <v>82859</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6187,21 +6187,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>835354</v>
+        <v>835241</v>
       </c>
       <c r="R55" t="n">
-        <v>7431995</v>
+        <v>7432287</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6261,12 +6261,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6277,32 +6277,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126895019</v>
+        <v>126895027</v>
       </c>
       <c r="B56" t="n">
-        <v>91280</v>
+        <v>58031</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>112</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>835295</v>
+        <v>835398</v>
       </c>
       <c r="R56" t="n">
-        <v>7431936</v>
+        <v>7431822</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6378,32 +6378,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126891218</v>
+        <v>126892870</v>
       </c>
       <c r="B57" t="n">
-        <v>92620</v>
+        <v>57821</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>835411</v>
+        <v>835300</v>
       </c>
       <c r="R57" t="n">
-        <v>7432011</v>
+        <v>7431922</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6463,12 +6463,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6479,45 +6479,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126891747</v>
+        <v>126895019</v>
       </c>
       <c r="B58" t="n">
-        <v>80025</v>
+        <v>91280</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6456</v>
+        <v>112</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>835247</v>
+        <v>835295</v>
       </c>
       <c r="R58" t="n">
-        <v>7432156</v>
+        <v>7431936</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6564,12 +6564,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6580,10 +6580,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126892867</v>
+        <v>126891218</v>
       </c>
       <c r="B59" t="n">
-        <v>56853</v>
+        <v>92620</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>835268</v>
+        <v>835411</v>
       </c>
       <c r="R59" t="n">
-        <v>7431964</v>
+        <v>7432011</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6653,11 +6653,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6670,12 +6665,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6686,10 +6681,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126895027</v>
+        <v>126891747</v>
       </c>
       <c r="B60" t="n">
-        <v>58031</v>
+        <v>80025</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6697,34 +6692,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>835398</v>
+        <v>835247</v>
       </c>
       <c r="R60" t="n">
-        <v>7431822</v>
+        <v>7432156</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6771,12 +6766,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6787,32 +6782,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892870</v>
+        <v>126892867</v>
       </c>
       <c r="B61" t="n">
-        <v>57821</v>
+        <v>56853</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6822,10 +6817,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>835300</v>
+        <v>835268</v>
       </c>
       <c r="R61" t="n">
-        <v>7431922</v>
+        <v>7431964</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6858,6 +6853,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7408,32 +7408,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126896051</v>
+        <v>126896458</v>
       </c>
       <c r="B67" t="n">
-        <v>98364</v>
+        <v>91280</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219790</v>
+        <v>112</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7443,10 +7443,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>835330</v>
+        <v>835425</v>
       </c>
       <c r="R67" t="n">
-        <v>7432131</v>
+        <v>7431979</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7476,9 +7476,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7493,12 +7503,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7509,32 +7519,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126896458</v>
+        <v>126896051</v>
       </c>
       <c r="B68" t="n">
-        <v>91280</v>
+        <v>98364</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>112</v>
+        <v>219790</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7544,10 +7554,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>835425</v>
+        <v>835330</v>
       </c>
       <c r="R68" t="n">
-        <v>7431979</v>
+        <v>7432131</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7577,19 +7587,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7604,12 +7604,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -9854,32 +9854,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126943157</v>
+        <v>126943156</v>
       </c>
       <c r="B91" t="n">
-        <v>77996</v>
+        <v>92620</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>835394</v>
+        <v>835445</v>
       </c>
       <c r="R91" t="n">
-        <v>7431928</v>
+        <v>7431908</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9955,32 +9955,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126943156</v>
+        <v>126943157</v>
       </c>
       <c r="B92" t="n">
-        <v>92620</v>
+        <v>77996</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>835445</v>
+        <v>835394</v>
       </c>
       <c r="R92" t="n">
-        <v>7431908</v>
+        <v>7431928</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -1202,32 +1202,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126892873</v>
+        <v>126896461</v>
       </c>
       <c r="B7" t="n">
-        <v>97331</v>
+        <v>78777</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>835237</v>
+        <v>835447</v>
       </c>
       <c r="R7" t="n">
-        <v>7431832</v>
+        <v>7431922</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,9 +1270,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,12 +1297,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1303,32 +1313,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126896461</v>
+        <v>126892873</v>
       </c>
       <c r="B8" t="n">
-        <v>78777</v>
+        <v>97331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>835447</v>
+        <v>835237</v>
       </c>
       <c r="R8" t="n">
-        <v>7431922</v>
+        <v>7431832</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,19 +1381,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,12 +1398,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1818,32 +1818,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126892879</v>
+        <v>126893108</v>
       </c>
       <c r="B13" t="n">
-        <v>98364</v>
+        <v>78685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>835250</v>
+        <v>835380</v>
       </c>
       <c r="R13" t="n">
-        <v>7432179</v>
+        <v>7431824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,12 +1903,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1919,45 +1919,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126893108</v>
+        <v>126895046</v>
       </c>
       <c r="B14" t="n">
-        <v>78685</v>
+        <v>92620</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>835380</v>
+        <v>835398</v>
       </c>
       <c r="R14" t="n">
-        <v>7431824</v>
+        <v>7431830</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,12 +2004,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2020,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126895046</v>
+        <v>126892879</v>
       </c>
       <c r="B15" t="n">
-        <v>92620</v>
+        <v>98364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2031,34 +2031,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>835398</v>
+        <v>835250</v>
       </c>
       <c r="R15" t="n">
-        <v>7431830</v>
+        <v>7432179</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,12 +2105,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2121,32 +2121,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126891788</v>
+        <v>126893087</v>
       </c>
       <c r="B16" t="n">
-        <v>78685</v>
+        <v>97331</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>835310</v>
+        <v>835357</v>
       </c>
       <c r="R16" t="n">
-        <v>7431905</v>
+        <v>7432179</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,12 +2206,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2222,32 +2222,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126893087</v>
+        <v>126891788</v>
       </c>
       <c r="B17" t="n">
-        <v>97331</v>
+        <v>78685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>835357</v>
+        <v>835310</v>
       </c>
       <c r="R17" t="n">
-        <v>7432179</v>
+        <v>7431905</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,12 +2307,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -3874,32 +3874,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126893092</v>
+        <v>126891743</v>
       </c>
       <c r="B33" t="n">
-        <v>97331</v>
+        <v>91350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>835234</v>
+        <v>835324</v>
       </c>
       <c r="R33" t="n">
-        <v>7432287</v>
+        <v>7431890</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3959,12 +3959,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3975,32 +3975,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126896220</v>
+        <v>126893092</v>
       </c>
       <c r="B34" t="n">
-        <v>82859</v>
+        <v>97331</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>835166</v>
+        <v>835234</v>
       </c>
       <c r="R34" t="n">
-        <v>7431954</v>
+        <v>7432287</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,19 +4043,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4070,12 +4060,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4086,10 +4076,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126891743</v>
+        <v>126896220</v>
       </c>
       <c r="B35" t="n">
-        <v>91350</v>
+        <v>82859</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4097,21 +4087,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4121,10 +4111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>835324</v>
+        <v>835166</v>
       </c>
       <c r="R35" t="n">
-        <v>7431890</v>
+        <v>7431954</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4154,9 +4144,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4171,12 +4171,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -5025,10 +5025,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126896207</v>
+        <v>126892874</v>
       </c>
       <c r="B44" t="n">
-        <v>79636</v>
+        <v>75142</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5036,21 +5036,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>835216</v>
+        <v>835180</v>
       </c>
       <c r="R44" t="n">
-        <v>7432256</v>
+        <v>7431962</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5093,19 +5093,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5120,12 +5110,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5136,10 +5126,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126892874</v>
+        <v>126896207</v>
       </c>
       <c r="B45" t="n">
-        <v>75142</v>
+        <v>79636</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5147,21 +5137,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5171,10 +5161,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>835180</v>
+        <v>835216</v>
       </c>
       <c r="R45" t="n">
-        <v>7431962</v>
+        <v>7432256</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5204,9 +5194,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5221,12 +5221,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -10571,32 +10571,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126943151</v>
+        <v>126943153</v>
       </c>
       <c r="B98" t="n">
-        <v>92620</v>
+        <v>98447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>835382</v>
+        <v>835440</v>
       </c>
       <c r="R98" t="n">
-        <v>7432189</v>
+        <v>7431856</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10672,32 +10672,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126943153</v>
+        <v>126943151</v>
       </c>
       <c r="B99" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>835440</v>
+        <v>835382</v>
       </c>
       <c r="R99" t="n">
-        <v>7431856</v>
+        <v>7432189</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -1202,32 +1202,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126896461</v>
+        <v>126892873</v>
       </c>
       <c r="B7" t="n">
-        <v>78777</v>
+        <v>97331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>835447</v>
+        <v>835237</v>
       </c>
       <c r="R7" t="n">
-        <v>7431922</v>
+        <v>7431832</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,19 +1270,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,12 +1287,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1313,32 +1303,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126892873</v>
+        <v>126896461</v>
       </c>
       <c r="B8" t="n">
-        <v>97331</v>
+        <v>78777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>835237</v>
+        <v>835447</v>
       </c>
       <c r="R8" t="n">
-        <v>7431832</v>
+        <v>7431922</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,9 +1371,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,12 +1398,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1414,32 +1414,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126893109</v>
+        <v>126896034</v>
       </c>
       <c r="B9" t="n">
-        <v>92620</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>835379</v>
+        <v>835299</v>
       </c>
       <c r="R9" t="n">
-        <v>7431868</v>
+        <v>7432168</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,12 +1499,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1515,32 +1515,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126896034</v>
+        <v>126893109</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>835299</v>
+        <v>835379</v>
       </c>
       <c r="R10" t="n">
-        <v>7432168</v>
+        <v>7431868</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,12 +1600,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1616,32 +1616,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126894504</v>
+        <v>126896048</v>
       </c>
       <c r="B11" t="n">
-        <v>92620</v>
+        <v>91591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>835249</v>
+        <v>835326</v>
       </c>
       <c r="R11" t="n">
-        <v>7431964</v>
+        <v>7431862</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,12 +1701,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1717,32 +1717,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126896048</v>
+        <v>126894504</v>
       </c>
       <c r="B12" t="n">
-        <v>91591</v>
+        <v>92620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>835326</v>
+        <v>835249</v>
       </c>
       <c r="R12" t="n">
-        <v>7431862</v>
+        <v>7431964</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,12 +1802,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2023,7 +2023,7 @@
         <v>126892879</v>
       </c>
       <c r="B15" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,32 +2121,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126893087</v>
+        <v>126891788</v>
       </c>
       <c r="B16" t="n">
-        <v>97331</v>
+        <v>78685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>835357</v>
+        <v>835310</v>
       </c>
       <c r="R16" t="n">
-        <v>7432179</v>
+        <v>7431905</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,12 +2206,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2222,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126891788</v>
+        <v>126896456</v>
       </c>
       <c r="B17" t="n">
-        <v>78685</v>
+        <v>79636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>835310</v>
+        <v>835435</v>
       </c>
       <c r="R17" t="n">
-        <v>7431905</v>
+        <v>7431927</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,9 +2290,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2307,12 +2317,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2323,32 +2333,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126896456</v>
+        <v>126893087</v>
       </c>
       <c r="B18" t="n">
-        <v>79636</v>
+        <v>97331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2358,10 +2368,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>835435</v>
+        <v>835357</v>
       </c>
       <c r="R18" t="n">
-        <v>7431927</v>
+        <v>7432179</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2391,19 +2401,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,12 +2418,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2434,32 +2434,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126891745</v>
+        <v>126896208</v>
       </c>
       <c r="B19" t="n">
-        <v>91280</v>
+        <v>97331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>835271</v>
+        <v>835253</v>
       </c>
       <c r="R19" t="n">
-        <v>7431952</v>
+        <v>7431988</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,9 +2502,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2519,12 +2529,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2535,32 +2545,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126896208</v>
+        <v>126891745</v>
       </c>
       <c r="B20" t="n">
-        <v>97331</v>
+        <v>91280</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>112</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>835253</v>
+        <v>835271</v>
       </c>
       <c r="R20" t="n">
-        <v>7431988</v>
+        <v>7431952</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2603,19 +2613,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2630,12 +2630,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2747,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126896462</v>
+        <v>126891737</v>
       </c>
       <c r="B22" t="n">
-        <v>78776</v>
+        <v>79636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2758,21 +2758,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>835438</v>
+        <v>835163</v>
       </c>
       <c r="R22" t="n">
-        <v>7431930</v>
+        <v>7431931</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,19 +2815,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2842,12 +2832,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2858,10 +2848,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126891737</v>
+        <v>126891211</v>
       </c>
       <c r="B23" t="n">
-        <v>79636</v>
+        <v>91280</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2869,21 +2859,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2893,10 +2883,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>835163</v>
+        <v>835367</v>
       </c>
       <c r="R23" t="n">
-        <v>7431931</v>
+        <v>7432211</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,12 +2933,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2959,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891211</v>
+        <v>126896462</v>
       </c>
       <c r="B24" t="n">
-        <v>91280</v>
+        <v>78776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,21 +2960,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>112</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>835367</v>
+        <v>835438</v>
       </c>
       <c r="R24" t="n">
-        <v>7432211</v>
+        <v>7431930</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3027,9 +3017,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3044,12 +3044,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3060,10 +3060,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126895020</v>
+        <v>126896216</v>
       </c>
       <c r="B25" t="n">
-        <v>91280</v>
+        <v>57821</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,34 +3071,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>112</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>835302</v>
+        <v>835232</v>
       </c>
       <c r="R25" t="n">
-        <v>7431967</v>
+        <v>7431857</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,9 +3128,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3145,12 +3155,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3161,45 +3171,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126896172</v>
+        <v>126895020</v>
       </c>
       <c r="B26" t="n">
-        <v>91591</v>
+        <v>91280</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>835412</v>
+        <v>835302</v>
       </c>
       <c r="R26" t="n">
-        <v>7431868</v>
+        <v>7431967</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3246,44 +3256,48 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126896052</v>
+        <v>126896172</v>
       </c>
       <c r="B27" t="n">
-        <v>92620</v>
+        <v>91591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3293,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>835305</v>
+        <v>835412</v>
       </c>
       <c r="R27" t="n">
-        <v>7431987</v>
+        <v>7431868</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3343,23 +3357,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126895047</v>
+        <v>126896052</v>
       </c>
       <c r="B28" t="n">
         <v>92620</v>
@@ -3390,14 +3400,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>835325</v>
+        <v>835305</v>
       </c>
       <c r="R28" t="n">
-        <v>7432027</v>
+        <v>7431987</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,12 +3454,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3460,45 +3470,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126896216</v>
+        <v>126895047</v>
       </c>
       <c r="B29" t="n">
-        <v>57821</v>
+        <v>92620</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>835232</v>
+        <v>835325</v>
       </c>
       <c r="R29" t="n">
-        <v>7431857</v>
+        <v>7432027</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3528,19 +3538,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3555,12 +3555,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3571,32 +3571,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126894482</v>
+        <v>126893081</v>
       </c>
       <c r="B30" t="n">
-        <v>97331</v>
+        <v>92624</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>4365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>835253</v>
+        <v>835404</v>
       </c>
       <c r="R30" t="n">
-        <v>7432159</v>
+        <v>7432008</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3656,12 +3656,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3773,32 +3773,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126893081</v>
+        <v>126894482</v>
       </c>
       <c r="B32" t="n">
-        <v>92624</v>
+        <v>97331</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4365</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>835404</v>
+        <v>835253</v>
       </c>
       <c r="R32" t="n">
-        <v>7432008</v>
+        <v>7432159</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3858,12 +3858,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4402,7 +4402,7 @@
         <v>126891761</v>
       </c>
       <c r="B38" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4601,32 +4601,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126896012</v>
+        <v>126896476</v>
       </c>
       <c r="B40" t="n">
-        <v>97325</v>
+        <v>78685</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>835330</v>
+        <v>835392</v>
       </c>
       <c r="R40" t="n">
-        <v>7432136</v>
+        <v>7431887</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4669,9 +4669,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4686,12 +4696,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4702,32 +4712,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126896476</v>
+        <v>126896015</v>
       </c>
       <c r="B41" t="n">
-        <v>78685</v>
+        <v>79042</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4737,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>835392</v>
+        <v>835346</v>
       </c>
       <c r="R41" t="n">
-        <v>7431887</v>
+        <v>7431909</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,19 +4780,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4797,12 +4797,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4813,10 +4813,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126896015</v>
+        <v>126896012</v>
       </c>
       <c r="B42" t="n">
-        <v>79042</v>
+        <v>97325</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4824,21 +4824,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>835346</v>
+        <v>835330</v>
       </c>
       <c r="R42" t="n">
-        <v>7431909</v>
+        <v>7432136</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,10 +5025,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126892874</v>
+        <v>126896207</v>
       </c>
       <c r="B44" t="n">
-        <v>75142</v>
+        <v>79636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5036,21 +5036,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>835180</v>
+        <v>835216</v>
       </c>
       <c r="R44" t="n">
-        <v>7431962</v>
+        <v>7432256</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5093,9 +5093,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5110,12 +5120,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5126,10 +5136,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126896207</v>
+        <v>126892874</v>
       </c>
       <c r="B45" t="n">
-        <v>79636</v>
+        <v>75142</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5137,21 +5147,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5161,10 +5171,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>835216</v>
+        <v>835180</v>
       </c>
       <c r="R45" t="n">
-        <v>7432256</v>
+        <v>7431962</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5194,19 +5204,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5221,12 +5221,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5338,10 +5338,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126891762</v>
+        <v>126896013</v>
       </c>
       <c r="B47" t="n">
-        <v>105484</v>
+        <v>97331</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>835361</v>
+        <v>835330</v>
       </c>
       <c r="R47" t="n">
-        <v>7431869</v>
+        <v>7431947</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5423,12 +5423,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5439,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126896013</v>
+        <v>126891762</v>
       </c>
       <c r="B48" t="n">
-        <v>97331</v>
+        <v>105486</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5450,21 +5450,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>835330</v>
+        <v>835361</v>
       </c>
       <c r="R48" t="n">
-        <v>7431947</v>
+        <v>7431869</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,12 +5524,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5762,10 +5762,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126893090</v>
+        <v>126896046</v>
       </c>
       <c r="B51" t="n">
-        <v>92612</v>
+        <v>82859</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5773,21 +5773,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4361</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5797,10 +5797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>835354</v>
+        <v>835241</v>
       </c>
       <c r="R51" t="n">
-        <v>7431995</v>
+        <v>7432287</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5847,12 +5847,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5863,45 +5863,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126896455</v>
+        <v>126895028</v>
       </c>
       <c r="B52" t="n">
-        <v>79636</v>
+        <v>91258</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>2013</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>835445</v>
+        <v>835423</v>
       </c>
       <c r="R52" t="n">
-        <v>7431926</v>
+        <v>7431886</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5931,19 +5931,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5958,12 +5948,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5974,32 +5964,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126893083</v>
+        <v>126893090</v>
       </c>
       <c r="B53" t="n">
-        <v>97325</v>
+        <v>92612</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6009,10 +5999,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>835458</v>
+        <v>835354</v>
       </c>
       <c r="R53" t="n">
-        <v>7431881</v>
+        <v>7431995</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6075,45 +6065,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126895028</v>
+        <v>126896455</v>
       </c>
       <c r="B54" t="n">
-        <v>91258</v>
+        <v>79636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2013</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>835423</v>
+        <v>835445</v>
       </c>
       <c r="R54" t="n">
-        <v>7431886</v>
+        <v>7431926</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6143,9 +6133,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6160,12 +6160,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6176,32 +6176,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126896046</v>
+        <v>126893083</v>
       </c>
       <c r="B55" t="n">
-        <v>82859</v>
+        <v>97325</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>835241</v>
+        <v>835458</v>
       </c>
       <c r="R55" t="n">
-        <v>7432287</v>
+        <v>7431881</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6261,12 +6261,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6277,32 +6277,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126895027</v>
+        <v>126895019</v>
       </c>
       <c r="B56" t="n">
-        <v>58031</v>
+        <v>91280</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>112</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>835398</v>
+        <v>835295</v>
       </c>
       <c r="R56" t="n">
-        <v>7431822</v>
+        <v>7431936</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6378,32 +6378,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126892870</v>
+        <v>126891218</v>
       </c>
       <c r="B57" t="n">
-        <v>57821</v>
+        <v>92620</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>835300</v>
+        <v>835411</v>
       </c>
       <c r="R57" t="n">
-        <v>7431922</v>
+        <v>7432011</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6463,12 +6463,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6479,45 +6479,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126895019</v>
+        <v>126891747</v>
       </c>
       <c r="B58" t="n">
-        <v>91280</v>
+        <v>80025</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>112</v>
+        <v>6456</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>835295</v>
+        <v>835247</v>
       </c>
       <c r="R58" t="n">
-        <v>7431936</v>
+        <v>7432156</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6564,12 +6564,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6580,10 +6580,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126891218</v>
+        <v>126892867</v>
       </c>
       <c r="B59" t="n">
-        <v>92620</v>
+        <v>56853</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>835411</v>
+        <v>835268</v>
       </c>
       <c r="R59" t="n">
-        <v>7432011</v>
+        <v>7431964</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6653,6 +6653,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6665,12 +6670,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6681,10 +6686,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126891747</v>
+        <v>126895027</v>
       </c>
       <c r="B60" t="n">
-        <v>80025</v>
+        <v>58031</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6692,34 +6697,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>835247</v>
+        <v>835398</v>
       </c>
       <c r="R60" t="n">
-        <v>7432156</v>
+        <v>7431822</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6766,12 +6771,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6782,32 +6787,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892867</v>
+        <v>126892870</v>
       </c>
       <c r="B61" t="n">
-        <v>56853</v>
+        <v>57821</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6817,10 +6822,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>835268</v>
+        <v>835300</v>
       </c>
       <c r="R61" t="n">
-        <v>7431964</v>
+        <v>7431922</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6853,11 +6858,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6891,7 +6891,7 @@
         <v>126896035</v>
       </c>
       <c r="B62" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6989,32 +6989,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126894490</v>
+        <v>126896458</v>
       </c>
       <c r="B63" t="n">
-        <v>91491</v>
+        <v>91280</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1503</v>
+        <v>112</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>835300</v>
+        <v>835425</v>
       </c>
       <c r="R63" t="n">
-        <v>7431907</v>
+        <v>7431979</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7057,9 +7057,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7074,12 +7084,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7090,32 +7100,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126896213</v>
+        <v>126894490</v>
       </c>
       <c r="B64" t="n">
-        <v>100602</v>
+        <v>91491</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1365</v>
+        <v>1503</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7125,10 +7135,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>835235</v>
+        <v>835300</v>
       </c>
       <c r="R64" t="n">
-        <v>7431827</v>
+        <v>7431907</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7158,19 +7168,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7185,12 +7185,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7201,10 +7201,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126892868</v>
+        <v>126896213</v>
       </c>
       <c r="B65" t="n">
-        <v>56853</v>
+        <v>100603</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7212,21 +7212,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>1365</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7236,10 +7236,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>835234</v>
+        <v>835235</v>
       </c>
       <c r="R65" t="n">
-        <v>7431879</v>
+        <v>7431827</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7269,14 +7269,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7291,12 +7296,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7307,32 +7312,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126894487</v>
+        <v>126892868</v>
       </c>
       <c r="B66" t="n">
-        <v>56844</v>
+        <v>56853</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7342,10 +7347,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>835105</v>
+        <v>835234</v>
       </c>
       <c r="R66" t="n">
-        <v>7432062</v>
+        <v>7431879</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,6 +7385,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7392,12 +7402,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7408,10 +7418,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126896458</v>
+        <v>126894487</v>
       </c>
       <c r="B67" t="n">
-        <v>91280</v>
+        <v>56844</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7419,21 +7429,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>112</v>
+        <v>102612</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7443,10 +7453,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>835425</v>
+        <v>835105</v>
       </c>
       <c r="R67" t="n">
-        <v>7431979</v>
+        <v>7432062</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7476,19 +7486,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7503,12 +7503,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7522,7 +7522,7 @@
         <v>126896051</v>
       </c>
       <c r="B68" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8614,10 +8614,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126915032</v>
+        <v>126915011</v>
       </c>
       <c r="B79" t="n">
-        <v>78424</v>
+        <v>91280</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8625,21 +8625,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6437</v>
+        <v>112</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>835212</v>
+        <v>835374</v>
       </c>
       <c r="R79" t="n">
-        <v>7432119</v>
+        <v>7432212</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126915011</v>
+        <v>126915032</v>
       </c>
       <c r="B80" t="n">
-        <v>91280</v>
+        <v>78424</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>112</v>
+        <v>6437</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>835374</v>
+        <v>835212</v>
       </c>
       <c r="R80" t="n">
-        <v>7432212</v>
+        <v>7432119</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10571,32 +10571,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126943153</v>
+        <v>126943151</v>
       </c>
       <c r="B98" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>835440</v>
+        <v>835382</v>
       </c>
       <c r="R98" t="n">
-        <v>7431856</v>
+        <v>7432189</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10672,32 +10672,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126943151</v>
+        <v>126943153</v>
       </c>
       <c r="B99" t="n">
-        <v>92620</v>
+        <v>98448</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>835382</v>
+        <v>835440</v>
       </c>
       <c r="R99" t="n">
-        <v>7432189</v>
+        <v>7431856</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10773,10 +10773,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127414787</v>
+        <v>127414788</v>
       </c>
       <c r="B100" t="n">
-        <v>92614</v>
+        <v>92612</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10784,21 +10784,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>835307</v>
+        <v>835310</v>
       </c>
       <c r="R100" t="n">
-        <v>7432078</v>
+        <v>7432075</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10879,10 +10879,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127414788</v>
+        <v>127414787</v>
       </c>
       <c r="B101" t="n">
-        <v>92612</v>
+        <v>92614</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10890,21 +10890,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10918,10 +10918,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>835310</v>
+        <v>835307</v>
       </c>
       <c r="R101" t="n">
-        <v>7432075</v>
+        <v>7432078</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -1414,32 +1414,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126896034</v>
+        <v>126893109</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>92620</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>835299</v>
+        <v>835379</v>
       </c>
       <c r="R9" t="n">
-        <v>7432168</v>
+        <v>7431868</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,12 +1499,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1515,32 +1515,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126893109</v>
+        <v>126896034</v>
       </c>
       <c r="B10" t="n">
-        <v>92620</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>835379</v>
+        <v>835299</v>
       </c>
       <c r="R10" t="n">
-        <v>7431868</v>
+        <v>7432168</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,12 +1600,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126895046</v>
+        <v>126892879</v>
       </c>
       <c r="B14" t="n">
-        <v>92620</v>
+        <v>98365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,34 +1930,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>835398</v>
+        <v>835250</v>
       </c>
       <c r="R14" t="n">
-        <v>7431830</v>
+        <v>7432179</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,12 +2004,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2020,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126892879</v>
+        <v>126895046</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>92620</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2031,34 +2031,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>835250</v>
+        <v>835398</v>
       </c>
       <c r="R15" t="n">
-        <v>7432179</v>
+        <v>7431830</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,12 +2105,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126896208</v>
+        <v>126896010</v>
       </c>
       <c r="B19" t="n">
-        <v>97331</v>
+        <v>56596</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>208255</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>835253</v>
+        <v>835133</v>
       </c>
       <c r="R19" t="n">
-        <v>7431988</v>
+        <v>7432014</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,19 +2502,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2529,12 +2519,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2545,32 +2535,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126891745</v>
+        <v>126896208</v>
       </c>
       <c r="B20" t="n">
-        <v>91280</v>
+        <v>97331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>112</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>835271</v>
+        <v>835253</v>
       </c>
       <c r="R20" t="n">
-        <v>7431952</v>
+        <v>7431988</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,9 +2603,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2630,12 +2630,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2646,32 +2646,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126896010</v>
+        <v>126891745</v>
       </c>
       <c r="B21" t="n">
-        <v>56596</v>
+        <v>91280</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208255</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>835133</v>
+        <v>835271</v>
       </c>
       <c r="R21" t="n">
-        <v>7432014</v>
+        <v>7431952</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2731,12 +2731,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2747,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126891737</v>
+        <v>126891211</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>91280</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2758,21 +2758,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>835163</v>
+        <v>835367</v>
       </c>
       <c r="R22" t="n">
-        <v>7431931</v>
+        <v>7432211</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,12 +2832,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2848,10 +2848,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126891211</v>
+        <v>126896462</v>
       </c>
       <c r="B23" t="n">
-        <v>91280</v>
+        <v>78776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,21 +2859,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>112</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2883,10 +2883,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>835367</v>
+        <v>835438</v>
       </c>
       <c r="R23" t="n">
-        <v>7432211</v>
+        <v>7431930</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2916,9 +2916,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2933,12 +2943,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2949,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126896462</v>
+        <v>126891737</v>
       </c>
       <c r="B24" t="n">
-        <v>78776</v>
+        <v>79636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2960,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>835438</v>
+        <v>835163</v>
       </c>
       <c r="R24" t="n">
-        <v>7431930</v>
+        <v>7431931</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3017,19 +3027,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3044,12 +3044,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3060,10 +3060,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126896216</v>
+        <v>126895020</v>
       </c>
       <c r="B25" t="n">
-        <v>57821</v>
+        <v>91280</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,34 +3071,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>112</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>835232</v>
+        <v>835302</v>
       </c>
       <c r="R25" t="n">
-        <v>7431857</v>
+        <v>7431967</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,19 +3128,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3155,12 +3145,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3171,45 +3161,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126895020</v>
+        <v>126896172</v>
       </c>
       <c r="B26" t="n">
-        <v>91280</v>
+        <v>91591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>835302</v>
+        <v>835412</v>
       </c>
       <c r="R26" t="n">
-        <v>7431967</v>
+        <v>7431868</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3256,48 +3246,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126896172</v>
+        <v>126896052</v>
       </c>
       <c r="B27" t="n">
-        <v>91591</v>
+        <v>92620</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3307,10 +3293,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>835412</v>
+        <v>835305</v>
       </c>
       <c r="R27" t="n">
-        <v>7431868</v>
+        <v>7431987</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,19 +3343,23 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126896052</v>
+        <v>126895047</v>
       </c>
       <c r="B28" t="n">
         <v>92620</v>
@@ -3400,14 +3390,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>835305</v>
+        <v>835325</v>
       </c>
       <c r="R28" t="n">
-        <v>7431987</v>
+        <v>7432027</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,12 +3444,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3470,45 +3460,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126895047</v>
+        <v>126896216</v>
       </c>
       <c r="B29" t="n">
-        <v>92620</v>
+        <v>57821</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>835325</v>
+        <v>835232</v>
       </c>
       <c r="R29" t="n">
-        <v>7432027</v>
+        <v>7431857</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,9 +3528,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3555,12 +3555,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3874,10 +3874,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126891743</v>
+        <v>126896220</v>
       </c>
       <c r="B33" t="n">
-        <v>91350</v>
+        <v>82859</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3885,21 +3885,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>835324</v>
+        <v>835166</v>
       </c>
       <c r="R33" t="n">
-        <v>7431890</v>
+        <v>7431954</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,9 +3942,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3959,12 +3969,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3975,32 +3985,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126893092</v>
+        <v>126896454</v>
       </c>
       <c r="B34" t="n">
-        <v>97331</v>
+        <v>79636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4010,10 +4020,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>835234</v>
+        <v>835391</v>
       </c>
       <c r="R34" t="n">
-        <v>7432287</v>
+        <v>7431880</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,9 +4053,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4060,12 +4080,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4076,10 +4096,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126896220</v>
+        <v>126891741</v>
       </c>
       <c r="B35" t="n">
-        <v>82859</v>
+        <v>57661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4087,21 +4107,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4111,10 +4131,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>835166</v>
+        <v>835254</v>
       </c>
       <c r="R35" t="n">
-        <v>7431954</v>
+        <v>7432142</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4144,19 +4164,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4171,12 +4181,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4187,10 +4197,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126896454</v>
+        <v>126891743</v>
       </c>
       <c r="B36" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4198,21 +4208,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4222,10 +4232,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>835391</v>
+        <v>835324</v>
       </c>
       <c r="R36" t="n">
-        <v>7431880</v>
+        <v>7431890</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,19 +4265,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4282,12 +4282,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4298,32 +4298,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126891741</v>
+        <v>126893092</v>
       </c>
       <c r="B37" t="n">
-        <v>57661</v>
+        <v>97331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>835254</v>
+        <v>835234</v>
       </c>
       <c r="R37" t="n">
-        <v>7432142</v>
+        <v>7432287</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4383,12 +4383,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -5762,32 +5762,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126896046</v>
+        <v>126893083</v>
       </c>
       <c r="B51" t="n">
-        <v>82859</v>
+        <v>97325</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5797,10 +5797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>835241</v>
+        <v>835458</v>
       </c>
       <c r="R51" t="n">
-        <v>7432287</v>
+        <v>7431881</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5847,12 +5847,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5863,45 +5863,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126895028</v>
+        <v>126896046</v>
       </c>
       <c r="B52" t="n">
-        <v>91258</v>
+        <v>82859</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2013</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>835423</v>
+        <v>835241</v>
       </c>
       <c r="R52" t="n">
-        <v>7431886</v>
+        <v>7432287</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5948,12 +5948,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5964,45 +5964,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126893090</v>
+        <v>126895028</v>
       </c>
       <c r="B53" t="n">
-        <v>92612</v>
+        <v>91258</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>2013</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>835354</v>
+        <v>835423</v>
       </c>
       <c r="R53" t="n">
-        <v>7431995</v>
+        <v>7431886</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6049,12 +6049,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6065,10 +6065,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126896455</v>
+        <v>126893090</v>
       </c>
       <c r="B54" t="n">
-        <v>79636</v>
+        <v>92612</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6076,21 +6076,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>835445</v>
+        <v>835354</v>
       </c>
       <c r="R54" t="n">
-        <v>7431926</v>
+        <v>7431995</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6133,19 +6133,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6160,12 +6150,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6176,32 +6166,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893083</v>
+        <v>126896455</v>
       </c>
       <c r="B55" t="n">
-        <v>97325</v>
+        <v>79636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6211,10 +6201,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>835458</v>
+        <v>835445</v>
       </c>
       <c r="R55" t="n">
-        <v>7431881</v>
+        <v>7431926</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6244,9 +6234,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6261,12 +6261,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6277,45 +6277,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126895019</v>
+        <v>126891747</v>
       </c>
       <c r="B56" t="n">
-        <v>91280</v>
+        <v>80025</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>112</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>835295</v>
+        <v>835247</v>
       </c>
       <c r="R56" t="n">
-        <v>7431936</v>
+        <v>7432156</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6362,12 +6362,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6378,10 +6378,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126891218</v>
+        <v>126892867</v>
       </c>
       <c r="B57" t="n">
-        <v>92620</v>
+        <v>56853</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6389,21 +6389,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>835411</v>
+        <v>835268</v>
       </c>
       <c r="R57" t="n">
-        <v>7432011</v>
+        <v>7431964</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6451,6 +6451,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6463,12 +6468,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6479,10 +6484,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126891747</v>
+        <v>126895027</v>
       </c>
       <c r="B58" t="n">
-        <v>80025</v>
+        <v>58031</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6490,34 +6495,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6456</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>835247</v>
+        <v>835398</v>
       </c>
       <c r="R58" t="n">
-        <v>7432156</v>
+        <v>7431822</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6564,12 +6569,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6580,45 +6585,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126892867</v>
+        <v>126895019</v>
       </c>
       <c r="B59" t="n">
-        <v>56853</v>
+        <v>91280</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>112</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>835268</v>
+        <v>835295</v>
       </c>
       <c r="R59" t="n">
-        <v>7431964</v>
+        <v>7431936</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6653,11 +6658,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6670,12 +6670,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6686,10 +6686,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126895027</v>
+        <v>126891218</v>
       </c>
       <c r="B60" t="n">
-        <v>58031</v>
+        <v>92620</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6697,34 +6697,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>835398</v>
+        <v>835411</v>
       </c>
       <c r="R60" t="n">
-        <v>7431822</v>
+        <v>7432011</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6771,12 +6771,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6787,32 +6787,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892870</v>
+        <v>126896035</v>
       </c>
       <c r="B61" t="n">
-        <v>57821</v>
+        <v>98448</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>835300</v>
+        <v>835290</v>
       </c>
       <c r="R61" t="n">
-        <v>7431922</v>
+        <v>7432175</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6872,12 +6872,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6888,32 +6888,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126896035</v>
+        <v>126892870</v>
       </c>
       <c r="B62" t="n">
-        <v>98448</v>
+        <v>57821</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6923,10 +6923,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>835290</v>
+        <v>835300</v>
       </c>
       <c r="R62" t="n">
-        <v>7432175</v>
+        <v>7431922</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6973,12 +6973,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -10773,10 +10773,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127414788</v>
+        <v>127414787</v>
       </c>
       <c r="B100" t="n">
-        <v>92612</v>
+        <v>92614</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10784,21 +10784,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>835310</v>
+        <v>835307</v>
       </c>
       <c r="R100" t="n">
-        <v>7432075</v>
+        <v>7432078</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10879,10 +10879,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127414787</v>
+        <v>127414788</v>
       </c>
       <c r="B101" t="n">
-        <v>92614</v>
+        <v>92612</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10890,21 +10890,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10918,10 +10918,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>835307</v>
+        <v>835310</v>
       </c>
       <c r="R101" t="n">
-        <v>7432078</v>
+        <v>7432075</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -1002,7 +1002,7 @@
         <v>126893107</v>
       </c>
       <c r="B5" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>126893073</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Pia Edfors, Caspar Ström, Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Ignacio Alvarez, Christina Boyd, per-erik mukka, Brian Johnson, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,7 +1205,7 @@
         <v>126892873</v>
       </c>
       <c r="B7" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>126896461</v>
       </c>
       <c r="B8" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>126893109</v>
       </c>
       <c r="B9" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>126896034</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>126896048</v>
       </c>
       <c r="B11" t="n">
-        <v>91591</v>
+        <v>91593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>126894504</v>
       </c>
       <c r="B12" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,45 +1818,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126893108</v>
+        <v>126895046</v>
       </c>
       <c r="B13" t="n">
-        <v>78685</v>
+        <v>92622</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>835380</v>
+        <v>835398</v>
       </c>
       <c r="R13" t="n">
-        <v>7431824</v>
+        <v>7431830</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,12 +1903,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1919,32 +1919,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126892879</v>
+        <v>126893108</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>78687</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>835250</v>
+        <v>835380</v>
       </c>
       <c r="R14" t="n">
-        <v>7432179</v>
+        <v>7431824</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,12 +2004,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2020,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126895046</v>
+        <v>126892879</v>
       </c>
       <c r="B15" t="n">
-        <v>92620</v>
+        <v>98367</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2031,34 +2031,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>835398</v>
+        <v>835250</v>
       </c>
       <c r="R15" t="n">
-        <v>7431830</v>
+        <v>7432179</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,12 +2105,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2124,7 +2124,7 @@
         <v>126891788</v>
       </c>
       <c r="B16" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>126896456</v>
       </c>
       <c r="B17" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>126893087</v>
       </c>
       <c r="B18" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Pia Edfors, Caspar Ström, Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Ignacio Alvarez, Christina Boyd, per-erik mukka, Brian Johnson, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126896010</v>
+        <v>126896208</v>
       </c>
       <c r="B19" t="n">
-        <v>56596</v>
+        <v>97333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208255</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>835133</v>
+        <v>835253</v>
       </c>
       <c r="R19" t="n">
-        <v>7432014</v>
+        <v>7431988</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,9 +2502,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2519,12 +2529,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Petra Wikström, Jenny Hjelm Córdoba, Jörgen Sundin, Louise Wolthers, Petya Valcheva, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2535,32 +2545,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126896208</v>
+        <v>126891745</v>
       </c>
       <c r="B20" t="n">
-        <v>97331</v>
+        <v>91282</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>112</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>835253</v>
+        <v>835271</v>
       </c>
       <c r="R20" t="n">
-        <v>7431988</v>
+        <v>7431952</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2603,19 +2613,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2630,12 +2630,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2646,32 +2646,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126891745</v>
+        <v>126896010</v>
       </c>
       <c r="B21" t="n">
-        <v>91280</v>
+        <v>56598</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>208255</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>835271</v>
+        <v>835133</v>
       </c>
       <c r="R21" t="n">
-        <v>7431952</v>
+        <v>7432014</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2731,12 +2731,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl, Louise Wolthers, Petya Valcheva, Jörgen Sundin, Petra Wikström, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2750,7 +2750,7 @@
         <v>126891211</v>
       </c>
       <c r="B22" t="n">
-        <v>91280</v>
+        <v>91282</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>126896462</v>
       </c>
       <c r="B23" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>126891737</v>
       </c>
       <c r="B24" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3060,10 +3060,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126895020</v>
+        <v>126896216</v>
       </c>
       <c r="B25" t="n">
-        <v>91280</v>
+        <v>57823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,34 +3071,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>112</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>835302</v>
+        <v>835232</v>
       </c>
       <c r="R25" t="n">
-        <v>7431967</v>
+        <v>7431857</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,9 +3128,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3145,12 +3155,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petra Wikström, Jenny Hjelm Córdoba, Jörgen Sundin, Louise Wolthers, Petya Valcheva, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3161,45 +3171,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126896172</v>
+        <v>126895020</v>
       </c>
       <c r="B26" t="n">
-        <v>91591</v>
+        <v>91282</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>835412</v>
+        <v>835302</v>
       </c>
       <c r="R26" t="n">
-        <v>7431868</v>
+        <v>7431967</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3246,44 +3256,48 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126896052</v>
+        <v>126896172</v>
       </c>
       <c r="B27" t="n">
-        <v>92620</v>
+        <v>91593</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3293,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>835305</v>
+        <v>835412</v>
       </c>
       <c r="R27" t="n">
-        <v>7431987</v>
+        <v>7431868</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3343,26 +3357,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126895047</v>
+        <v>126896052</v>
       </c>
       <c r="B28" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3390,14 +3400,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>835325</v>
+        <v>835305</v>
       </c>
       <c r="R28" t="n">
-        <v>7432027</v>
+        <v>7431987</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,12 +3454,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3460,45 +3470,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126896216</v>
+        <v>126895047</v>
       </c>
       <c r="B29" t="n">
-        <v>57821</v>
+        <v>92622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>835232</v>
+        <v>835325</v>
       </c>
       <c r="R29" t="n">
-        <v>7431857</v>
+        <v>7432027</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3528,19 +3538,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3555,12 +3555,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3571,10 +3571,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126893081</v>
+        <v>126895037</v>
       </c>
       <c r="B30" t="n">
-        <v>92624</v>
+        <v>91493</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3582,34 +3582,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>835404</v>
+        <v>835296</v>
       </c>
       <c r="R30" t="n">
-        <v>7432008</v>
+        <v>7431963</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3656,12 +3656,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3672,10 +3672,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126895037</v>
+        <v>126893081</v>
       </c>
       <c r="B31" t="n">
-        <v>91491</v>
+        <v>92626</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3683,34 +3683,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>835296</v>
+        <v>835404</v>
       </c>
       <c r="R31" t="n">
-        <v>7431963</v>
+        <v>7432008</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3757,12 +3757,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors, Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Ignacio Alvarez, Christina Boyd, per-erik mukka, Brian Johnson, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3776,7 +3776,7 @@
         <v>126894482</v>
       </c>
       <c r="B32" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>126896220</v>
       </c>
       <c r="B33" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström, Jenny Hjelm Córdoba, Jörgen Sundin, Louise Wolthers, Petya Valcheva, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3985,10 +3985,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126896454</v>
+        <v>126891741</v>
       </c>
       <c r="B34" t="n">
-        <v>79636</v>
+        <v>57663</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>835391</v>
+        <v>835254</v>
       </c>
       <c r="R34" t="n">
-        <v>7431880</v>
+        <v>7432142</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,19 +4053,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4080,12 +4070,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4096,10 +4086,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126891741</v>
+        <v>126891743</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>91352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4107,21 +4097,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4131,10 +4121,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>835254</v>
+        <v>835324</v>
       </c>
       <c r="R35" t="n">
-        <v>7432142</v>
+        <v>7431890</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4197,10 +4187,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126891743</v>
+        <v>126896454</v>
       </c>
       <c r="B36" t="n">
-        <v>91350</v>
+        <v>79638</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4208,21 +4198,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4232,10 +4222,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>835324</v>
+        <v>835391</v>
       </c>
       <c r="R36" t="n">
-        <v>7431890</v>
+        <v>7431880</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,9 +4255,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4282,12 +4282,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4301,7 +4301,7 @@
         <v>126893092</v>
       </c>
       <c r="B37" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Pia Edfors, Caspar Ström, Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Ignacio Alvarez, Christina Boyd, per-erik mukka, Brian Johnson, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4402,7 +4402,7 @@
         <v>126891761</v>
       </c>
       <c r="B38" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>126895021</v>
       </c>
       <c r="B39" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4601,32 +4601,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126896476</v>
+        <v>126896015</v>
       </c>
       <c r="B40" t="n">
-        <v>78685</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>835392</v>
+        <v>835346</v>
       </c>
       <c r="R40" t="n">
-        <v>7431887</v>
+        <v>7431909</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4669,19 +4669,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4696,12 +4686,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4712,32 +4702,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126896015</v>
+        <v>126896476</v>
       </c>
       <c r="B41" t="n">
-        <v>79042</v>
+        <v>78687</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4747,10 +4737,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>835346</v>
+        <v>835392</v>
       </c>
       <c r="R41" t="n">
-        <v>7431909</v>
+        <v>7431887</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,9 +4770,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4797,12 +4797,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4816,7 +4816,7 @@
         <v>126896012</v>
       </c>
       <c r="B42" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>126896215</v>
       </c>
       <c r="B43" t="n">
-        <v>95304</v>
+        <v>95306</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström, Jenny Hjelm Córdoba, Jörgen Sundin, Louise Wolthers, Petya Valcheva, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5025,10 +5025,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126896207</v>
+        <v>126892874</v>
       </c>
       <c r="B44" t="n">
-        <v>79636</v>
+        <v>75144</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5036,21 +5036,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>835216</v>
+        <v>835180</v>
       </c>
       <c r="R44" t="n">
-        <v>7432256</v>
+        <v>7431962</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5093,19 +5093,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5120,12 +5110,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5136,10 +5126,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126892874</v>
+        <v>126896207</v>
       </c>
       <c r="B45" t="n">
-        <v>75142</v>
+        <v>79638</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5147,21 +5137,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5171,10 +5161,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>835180</v>
+        <v>835216</v>
       </c>
       <c r="R45" t="n">
-        <v>7431962</v>
+        <v>7432256</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5204,9 +5194,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5221,12 +5221,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Petra Wikström, Jenny Hjelm Córdoba, Jörgen Sundin, Louise Wolthers, Petya Valcheva, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5240,7 +5240,7 @@
         <v>126896001</v>
       </c>
       <c r="B46" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>126896013</v>
       </c>
       <c r="B47" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Cecilia Goldkuhl, Louise Wolthers, Petya Valcheva, Jörgen Sundin, Petra Wikström, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5442,7 +5442,7 @@
         <v>126891762</v>
       </c>
       <c r="B48" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>126896453</v>
       </c>
       <c r="B49" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>126896459</v>
       </c>
       <c r="B50" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5762,32 +5762,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126893083</v>
+        <v>126896046</v>
       </c>
       <c r="B51" t="n">
-        <v>97325</v>
+        <v>82861</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5797,10 +5797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>835458</v>
+        <v>835241</v>
       </c>
       <c r="R51" t="n">
-        <v>7431881</v>
+        <v>7432287</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5847,12 +5847,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5863,45 +5863,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126896046</v>
+        <v>126895028</v>
       </c>
       <c r="B52" t="n">
-        <v>82859</v>
+        <v>91260</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>2013</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>835241</v>
+        <v>835423</v>
       </c>
       <c r="R52" t="n">
-        <v>7432287</v>
+        <v>7431886</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5948,12 +5948,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5964,45 +5964,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126895028</v>
+        <v>126893090</v>
       </c>
       <c r="B53" t="n">
-        <v>91258</v>
+        <v>92614</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2013</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>835423</v>
+        <v>835354</v>
       </c>
       <c r="R53" t="n">
-        <v>7431886</v>
+        <v>7431995</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6049,12 +6049,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors, Caspar Ström, Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Ignacio Alvarez, Christina Boyd, per-erik mukka, Brian Johnson, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6065,10 +6065,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126893090</v>
+        <v>126896455</v>
       </c>
       <c r="B54" t="n">
-        <v>92612</v>
+        <v>79638</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6076,21 +6076,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>835354</v>
+        <v>835445</v>
       </c>
       <c r="R54" t="n">
-        <v>7431995</v>
+        <v>7431926</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6133,9 +6133,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6150,12 +6160,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6166,32 +6176,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126896455</v>
+        <v>126893083</v>
       </c>
       <c r="B55" t="n">
-        <v>79636</v>
+        <v>97327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6201,10 +6211,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>835445</v>
+        <v>835458</v>
       </c>
       <c r="R55" t="n">
-        <v>7431926</v>
+        <v>7431881</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6234,19 +6244,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6261,12 +6261,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Pia Edfors, Caspar Ström, Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Ignacio Alvarez, Christina Boyd, per-erik mukka, Brian Johnson, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6277,45 +6277,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126891747</v>
+        <v>126895019</v>
       </c>
       <c r="B56" t="n">
-        <v>80025</v>
+        <v>91282</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>112</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>835247</v>
+        <v>835295</v>
       </c>
       <c r="R56" t="n">
-        <v>7432156</v>
+        <v>7431936</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6362,12 +6362,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6378,10 +6378,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126892867</v>
+        <v>126891747</v>
       </c>
       <c r="B57" t="n">
-        <v>56853</v>
+        <v>80027</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6389,21 +6389,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>835268</v>
+        <v>835247</v>
       </c>
       <c r="R57" t="n">
-        <v>7431964</v>
+        <v>7432156</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6451,11 +6451,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6468,12 +6463,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6484,45 +6479,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126895027</v>
+        <v>126892870</v>
       </c>
       <c r="B58" t="n">
-        <v>58031</v>
+        <v>57823</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>835398</v>
+        <v>835300</v>
       </c>
       <c r="R58" t="n">
-        <v>7431822</v>
+        <v>7431922</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6569,12 +6564,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6585,32 +6580,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126895019</v>
+        <v>126895027</v>
       </c>
       <c r="B59" t="n">
-        <v>91280</v>
+        <v>58033</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>112</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6620,10 +6615,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>835295</v>
+        <v>835398</v>
       </c>
       <c r="R59" t="n">
-        <v>7431936</v>
+        <v>7431822</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6686,32 +6681,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126891218</v>
+        <v>126896035</v>
       </c>
       <c r="B60" t="n">
-        <v>92620</v>
+        <v>98450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6721,10 +6716,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>835411</v>
+        <v>835290</v>
       </c>
       <c r="R60" t="n">
-        <v>7432011</v>
+        <v>7432175</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6771,12 +6766,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6787,32 +6782,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126896035</v>
+        <v>126891218</v>
       </c>
       <c r="B61" t="n">
-        <v>98448</v>
+        <v>92622</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6822,10 +6817,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>835290</v>
+        <v>835411</v>
       </c>
       <c r="R61" t="n">
-        <v>7432175</v>
+        <v>7432011</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6872,12 +6867,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6888,32 +6883,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126892870</v>
+        <v>126892867</v>
       </c>
       <c r="B62" t="n">
-        <v>57821</v>
+        <v>56855</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6923,10 +6918,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>835300</v>
+        <v>835268</v>
       </c>
       <c r="R62" t="n">
-        <v>7431922</v>
+        <v>7431964</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6959,6 +6954,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6992,7 +6992,7 @@
         <v>126896458</v>
       </c>
       <c r="B63" t="n">
-        <v>91280</v>
+        <v>91282</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>126894490</v>
       </c>
       <c r="B64" t="n">
-        <v>91491</v>
+        <v>91493</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>126896213</v>
       </c>
       <c r="B65" t="n">
-        <v>100603</v>
+        <v>100605</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström, Jenny Hjelm Córdoba, Jörgen Sundin, Louise Wolthers, Petya Valcheva, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7315,7 +7315,7 @@
         <v>126892868</v>
       </c>
       <c r="B66" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7418,32 +7418,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126894487</v>
+        <v>126896051</v>
       </c>
       <c r="B67" t="n">
-        <v>56844</v>
+        <v>98367</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102612</v>
+        <v>219790</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7453,10 +7453,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>835105</v>
+        <v>835330</v>
       </c>
       <c r="R67" t="n">
-        <v>7432062</v>
+        <v>7432131</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7503,12 +7503,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7519,32 +7519,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126896051</v>
+        <v>126894487</v>
       </c>
       <c r="B68" t="n">
-        <v>98365</v>
+        <v>56846</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>835330</v>
+        <v>835105</v>
       </c>
       <c r="R68" t="n">
-        <v>7432131</v>
+        <v>7432062</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7604,12 +7604,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7620,10 +7620,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126915007</v>
+        <v>126915556</v>
       </c>
       <c r="B69" t="n">
-        <v>79636</v>
+        <v>57823</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7631,31 +7631,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>835444</v>
+        <v>835394</v>
       </c>
       <c r="R69" t="n">
         <v>7431868</v>
@@ -7705,26 +7705,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126915556</v>
+        <v>126915007</v>
       </c>
       <c r="B70" t="n">
-        <v>57821</v>
+        <v>79638</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7732,31 +7728,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>835394</v>
+        <v>835444</v>
       </c>
       <c r="R70" t="n">
         <v>7431868</v>
@@ -7806,22 +7802,26 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>126894627</v>
       </c>
       <c r="B71" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>126915557</v>
       </c>
       <c r="B72" t="n">
-        <v>92632</v>
+        <v>92634</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126894632</v>
+        <v>126915019</v>
       </c>
       <c r="B73" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>835406</v>
+        <v>835275</v>
       </c>
       <c r="R73" t="n">
-        <v>7431965</v>
+        <v>7432030</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8101,12 +8101,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8117,45 +8117,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126915019</v>
+        <v>126915568</v>
       </c>
       <c r="B74" t="n">
-        <v>92813</v>
+        <v>92622</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>835275</v>
+        <v>835341</v>
       </c>
       <c r="R74" t="n">
-        <v>7432030</v>
+        <v>7432052</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8202,61 +8202,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126915568</v>
+        <v>126894632</v>
       </c>
       <c r="B75" t="n">
-        <v>92620</v>
+        <v>92815</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>835341</v>
+        <v>835406</v>
       </c>
       <c r="R75" t="n">
-        <v>7432052</v>
+        <v>7431965</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8303,22 +8299,26 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>126915562</v>
       </c>
       <c r="B76" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>126915015</v>
       </c>
       <c r="B77" t="n">
-        <v>79042</v>
+        <v>79044</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8513,10 +8513,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126894633</v>
+        <v>126915011</v>
       </c>
       <c r="B78" t="n">
-        <v>78777</v>
+        <v>91282</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8524,21 +8524,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>112</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>835411</v>
+        <v>835374</v>
       </c>
       <c r="R78" t="n">
-        <v>7431972</v>
+        <v>7432212</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8598,12 +8598,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8614,10 +8614,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126915011</v>
+        <v>126894633</v>
       </c>
       <c r="B79" t="n">
-        <v>91280</v>
+        <v>78779</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8625,21 +8625,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>112</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>835374</v>
+        <v>835411</v>
       </c>
       <c r="R79" t="n">
-        <v>7432212</v>
+        <v>7431972</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8699,12 +8699,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8718,7 +8718,7 @@
         <v>126915032</v>
       </c>
       <c r="B80" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>126915016</v>
       </c>
       <c r="B81" t="n">
-        <v>79042</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>126894643</v>
       </c>
       <c r="B82" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>126916087</v>
       </c>
       <c r="B83" t="n">
-        <v>92646</v>
+        <v>92648</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>126915017</v>
       </c>
       <c r="B84" t="n">
-        <v>79042</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>126927927</v>
       </c>
       <c r="B85" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>126927910</v>
       </c>
       <c r="B86" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>126891792</v>
       </c>
       <c r="B87" t="n">
-        <v>79988</v>
+        <v>79990</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>126927931</v>
       </c>
       <c r="B88" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>126943155</v>
       </c>
       <c r="B89" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>126943164</v>
       </c>
       <c r="B90" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>126943156</v>
       </c>
       <c r="B91" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>126943157</v>
       </c>
       <c r="B92" t="n">
-        <v>77996</v>
+        <v>77998</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>126943160</v>
       </c>
       <c r="B93" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>126943150</v>
       </c>
       <c r="B94" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>126943163</v>
       </c>
       <c r="B95" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>126943159</v>
       </c>
       <c r="B96" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>126943161</v>
       </c>
       <c r="B97" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10571,32 +10571,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126943151</v>
+        <v>126943153</v>
       </c>
       <c r="B98" t="n">
-        <v>92620</v>
+        <v>98450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>835382</v>
+        <v>835440</v>
       </c>
       <c r="R98" t="n">
-        <v>7432189</v>
+        <v>7431856</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10672,32 +10672,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126943153</v>
+        <v>126943151</v>
       </c>
       <c r="B99" t="n">
-        <v>98448</v>
+        <v>92622</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>835440</v>
+        <v>835382</v>
       </c>
       <c r="R99" t="n">
-        <v>7431856</v>
+        <v>7432189</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10776,7 +10776,7 @@
         <v>127414787</v>
       </c>
       <c r="B100" t="n">
-        <v>92614</v>
+        <v>92616</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>127414788</v>
       </c>
       <c r="B101" t="n">
-        <v>92612</v>
+        <v>92614</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -7620,10 +7620,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126915556</v>
+        <v>126915007</v>
       </c>
       <c r="B69" t="n">
-        <v>57823</v>
+        <v>79638</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7631,31 +7631,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>835394</v>
+        <v>835444</v>
       </c>
       <c r="R69" t="n">
         <v>7431868</v>
@@ -7705,22 +7705,26 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126915007</v>
+        <v>126915556</v>
       </c>
       <c r="B70" t="n">
-        <v>79638</v>
+        <v>57823</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7728,31 +7732,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>835444</v>
+        <v>835394</v>
       </c>
       <c r="R70" t="n">
         <v>7431868</v>
@@ -7802,19 +7806,15 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8016,7 +8016,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126915019</v>
+        <v>126894632</v>
       </c>
       <c r="B73" t="n">
         <v>92815</v>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>835275</v>
+        <v>835406</v>
       </c>
       <c r="R73" t="n">
-        <v>7432030</v>
+        <v>7431965</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8101,12 +8101,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8214,7 +8214,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126894632</v>
+        <v>126915019</v>
       </c>
       <c r="B75" t="n">
         <v>92815</v>
@@ -8249,10 +8249,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>835406</v>
+        <v>835275</v>
       </c>
       <c r="R75" t="n">
-        <v>7431965</v>
+        <v>7432030</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8299,12 +8299,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8513,10 +8513,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126915011</v>
+        <v>126894633</v>
       </c>
       <c r="B78" t="n">
-        <v>91282</v>
+        <v>78779</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8524,21 +8524,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>112</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>835374</v>
+        <v>835411</v>
       </c>
       <c r="R78" t="n">
-        <v>7432212</v>
+        <v>7431972</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8598,12 +8598,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8614,10 +8614,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126894633</v>
+        <v>126915011</v>
       </c>
       <c r="B79" t="n">
-        <v>78779</v>
+        <v>91282</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8625,21 +8625,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>112</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>835411</v>
+        <v>835374</v>
       </c>
       <c r="R79" t="n">
-        <v>7431972</v>
+        <v>7432212</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8699,12 +8699,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -10571,32 +10571,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126943153</v>
+        <v>126943151</v>
       </c>
       <c r="B98" t="n">
-        <v>98450</v>
+        <v>92622</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>835440</v>
+        <v>835382</v>
       </c>
       <c r="R98" t="n">
-        <v>7431856</v>
+        <v>7432189</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10672,32 +10672,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126943151</v>
+        <v>126943153</v>
       </c>
       <c r="B99" t="n">
-        <v>92622</v>
+        <v>98450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>835382</v>
+        <v>835440</v>
       </c>
       <c r="R99" t="n">
-        <v>7432189</v>
+        <v>7431856</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10773,10 +10773,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127414787</v>
+        <v>127414788</v>
       </c>
       <c r="B100" t="n">
-        <v>92616</v>
+        <v>92614</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10784,21 +10784,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>835307</v>
+        <v>835310</v>
       </c>
       <c r="R100" t="n">
-        <v>7432078</v>
+        <v>7432075</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10879,10 +10879,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127414788</v>
+        <v>127414787</v>
       </c>
       <c r="B101" t="n">
-        <v>92614</v>
+        <v>92616</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10890,21 +10890,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10918,10 +10918,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>835310</v>
+        <v>835307</v>
       </c>
       <c r="R101" t="n">
-        <v>7432075</v>
+        <v>7432078</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -10571,32 +10571,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126943151</v>
+        <v>126943153</v>
       </c>
       <c r="B98" t="n">
-        <v>92622</v>
+        <v>98450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>835382</v>
+        <v>835440</v>
       </c>
       <c r="R98" t="n">
-        <v>7432189</v>
+        <v>7431856</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10672,32 +10672,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126943153</v>
+        <v>126943151</v>
       </c>
       <c r="B99" t="n">
-        <v>98450</v>
+        <v>92622</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>835440</v>
+        <v>835382</v>
       </c>
       <c r="R99" t="n">
-        <v>7431856</v>
+        <v>7432189</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -9742,7 +9742,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
+          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -10776,7 +10776,7 @@
         <v>127414788</v>
       </c>
       <c r="B100" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>127414787</v>
       </c>
       <c r="B101" t="n">
-        <v>92616</v>
+        <v>92622</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -10776,7 +10776,7 @@
         <v>127414788</v>
       </c>
       <c r="B100" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>127414787</v>
       </c>
       <c r="B101" t="n">
-        <v>92622</v>
+        <v>92625</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -10776,7 +10776,7 @@
         <v>127414788</v>
       </c>
       <c r="B100" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>127414787</v>
       </c>
       <c r="B101" t="n">
-        <v>92625</v>
+        <v>92633</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -10776,7 +10776,7 @@
         <v>127414788</v>
       </c>
       <c r="B100" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>127414787</v>
       </c>
       <c r="B101" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -10773,10 +10773,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127414788</v>
+        <v>127414787</v>
       </c>
       <c r="B100" t="n">
-        <v>92632</v>
+        <v>92635</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10784,21 +10784,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>835310</v>
+        <v>835307</v>
       </c>
       <c r="R100" t="n">
-        <v>7432075</v>
+        <v>7432078</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10879,10 +10879,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127414787</v>
+        <v>127414788</v>
       </c>
       <c r="B101" t="n">
-        <v>92634</v>
+        <v>92633</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10890,21 +10890,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10918,10 +10918,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>835307</v>
+        <v>835310</v>
       </c>
       <c r="R101" t="n">
-        <v>7432078</v>
+        <v>7432075</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -10776,7 +10776,7 @@
         <v>127414787</v>
       </c>
       <c r="B100" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>127414788</v>
       </c>
       <c r="B101" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -1002,7 +1002,7 @@
         <v>126893107</v>
       </c>
       <c r="B5" t="n">
-        <v>78687</v>
+        <v>78678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>126893073</v>
       </c>
       <c r="B6" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pia Edfors, Caspar Ström, Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Ignacio Alvarez, Christina Boyd, per-erik mukka, Brian Johnson, Carin von Köhler</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,7 +1205,7 @@
         <v>126892873</v>
       </c>
       <c r="B7" t="n">
-        <v>97333</v>
+        <v>97320</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Jenny Hjelm Córdoba, Petya Valcheva, Petra Wikström, Jörgen Sundin, Louise Wolthers, Cecilia Goldkuhl, Petya Valcheva, Petra Wikström, Jörgen Sundin, Louise Wolthers, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1306,7 +1306,7 @@
         <v>126896461</v>
       </c>
       <c r="B8" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>126893109</v>
       </c>
       <c r="B9" t="n">
-        <v>92622</v>
+        <v>92609</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>126896034</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>126896048</v>
       </c>
       <c r="B11" t="n">
-        <v>91593</v>
+        <v>91580</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>126894504</v>
       </c>
       <c r="B12" t="n">
-        <v>92622</v>
+        <v>92609</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>126895046</v>
       </c>
       <c r="B13" t="n">
-        <v>92622</v>
+        <v>92609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,32 +1919,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126893108</v>
+        <v>126892879</v>
       </c>
       <c r="B14" t="n">
-        <v>78687</v>
+        <v>98353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>835380</v>
+        <v>835250</v>
       </c>
       <c r="R14" t="n">
-        <v>7431824</v>
+        <v>7432179</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,12 +2004,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
+          <t>Jenny Hjelm Córdoba, Petya Valcheva, Petra Wikström, Jörgen Sundin, Louise Wolthers, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2020,32 +2020,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126892879</v>
+        <v>126893108</v>
       </c>
       <c r="B15" t="n">
-        <v>98367</v>
+        <v>78678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>835250</v>
+        <v>835380</v>
       </c>
       <c r="R15" t="n">
-        <v>7432179</v>
+        <v>7431824</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,12 +2105,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2124,7 +2124,7 @@
         <v>126891788</v>
       </c>
       <c r="B16" t="n">
-        <v>78687</v>
+        <v>78678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>126896456</v>
       </c>
       <c r="B17" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>126893087</v>
       </c>
       <c r="B18" t="n">
-        <v>97333</v>
+        <v>97320</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pia Edfors, Caspar Ström, Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Ignacio Alvarez, Christina Boyd, per-erik mukka, Brian Johnson, Carin von Köhler</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2437,7 +2437,7 @@
         <v>126896208</v>
       </c>
       <c r="B19" t="n">
-        <v>97333</v>
+        <v>97320</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Petra Wikström, Jenny Hjelm Córdoba, Jörgen Sundin, Louise Wolthers, Petya Valcheva, Cecilia Goldkuhl</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>126891745</v>
       </c>
       <c r="B20" t="n">
-        <v>91282</v>
+        <v>91269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>126896010</v>
       </c>
       <c r="B21" t="n">
-        <v>56598</v>
+        <v>56592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Louise Wolthers, Petya Valcheva, Jörgen Sundin, Petra Wikström, Jenny Hjelm Córdoba</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2750,7 +2750,7 @@
         <v>126891211</v>
       </c>
       <c r="B22" t="n">
-        <v>91282</v>
+        <v>91269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>126896462</v>
       </c>
       <c r="B23" t="n">
-        <v>78778</v>
+        <v>78769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>126891737</v>
       </c>
       <c r="B24" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3060,10 +3060,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126896216</v>
+        <v>126895020</v>
       </c>
       <c r="B25" t="n">
-        <v>57823</v>
+        <v>91269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,34 +3071,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>112</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>835232</v>
+        <v>835302</v>
       </c>
       <c r="R25" t="n">
-        <v>7431857</v>
+        <v>7431967</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,19 +3128,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3155,12 +3145,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Petra Wikström, Jenny Hjelm Córdoba, Jörgen Sundin, Louise Wolthers, Petya Valcheva, Cecilia Goldkuhl</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3171,45 +3161,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126895020</v>
+        <v>126896172</v>
       </c>
       <c r="B26" t="n">
-        <v>91282</v>
+        <v>91580</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>835302</v>
+        <v>835412</v>
       </c>
       <c r="R26" t="n">
-        <v>7431967</v>
+        <v>7431868</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3256,48 +3246,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126896172</v>
+        <v>126896052</v>
       </c>
       <c r="B27" t="n">
-        <v>91593</v>
+        <v>92609</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3307,10 +3293,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>835412</v>
+        <v>835305</v>
       </c>
       <c r="R27" t="n">
-        <v>7431868</v>
+        <v>7431987</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,22 +3343,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126896052</v>
+        <v>126895047</v>
       </c>
       <c r="B28" t="n">
-        <v>92622</v>
+        <v>92609</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3400,14 +3390,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>835305</v>
+        <v>835325</v>
       </c>
       <c r="R28" t="n">
-        <v>7431987</v>
+        <v>7432027</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,12 +3444,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3470,45 +3460,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126895047</v>
+        <v>126896216</v>
       </c>
       <c r="B29" t="n">
-        <v>92622</v>
+        <v>57817</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>835325</v>
+        <v>835232</v>
       </c>
       <c r="R29" t="n">
-        <v>7432027</v>
+        <v>7431857</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,9 +3528,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3555,12 +3555,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3571,45 +3571,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126895037</v>
+        <v>126894482</v>
       </c>
       <c r="B30" t="n">
-        <v>91493</v>
+        <v>97320</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>835296</v>
+        <v>835253</v>
       </c>
       <c r="R30" t="n">
-        <v>7431963</v>
+        <v>7432159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3656,12 +3656,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3672,10 +3672,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126893081</v>
+        <v>126895037</v>
       </c>
       <c r="B31" t="n">
-        <v>92626</v>
+        <v>91480</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3683,34 +3683,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>835404</v>
+        <v>835296</v>
       </c>
       <c r="R31" t="n">
-        <v>7432008</v>
+        <v>7431963</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3757,12 +3757,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Pia Edfors, Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Ignacio Alvarez, Christina Boyd, per-erik mukka, Brian Johnson, Carin von Köhler</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3773,32 +3773,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126894482</v>
+        <v>126893081</v>
       </c>
       <c r="B32" t="n">
-        <v>97333</v>
+        <v>92613</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>4365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>835253</v>
+        <v>835404</v>
       </c>
       <c r="R32" t="n">
-        <v>7432159</v>
+        <v>7432008</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3858,12 +3858,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3877,7 +3877,7 @@
         <v>126896220</v>
       </c>
       <c r="B33" t="n">
-        <v>82861</v>
+        <v>82852</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Petra Wikström, Jenny Hjelm Córdoba, Jörgen Sundin, Louise Wolthers, Petya Valcheva, Cecilia Goldkuhl</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3985,10 +3985,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126891741</v>
+        <v>126891743</v>
       </c>
       <c r="B34" t="n">
-        <v>57663</v>
+        <v>91339</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>835254</v>
+        <v>835324</v>
       </c>
       <c r="R34" t="n">
-        <v>7432142</v>
+        <v>7431890</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126891743</v>
+        <v>126896454</v>
       </c>
       <c r="B35" t="n">
-        <v>91352</v>
+        <v>79629</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4097,21 +4097,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>835324</v>
+        <v>835391</v>
       </c>
       <c r="R35" t="n">
-        <v>7431890</v>
+        <v>7431880</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4154,9 +4154,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4171,12 +4181,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4187,10 +4197,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126896454</v>
+        <v>126891741</v>
       </c>
       <c r="B36" t="n">
-        <v>79638</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4198,21 +4208,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4222,10 +4232,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>835391</v>
+        <v>835254</v>
       </c>
       <c r="R36" t="n">
-        <v>7431880</v>
+        <v>7432142</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,19 +4265,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4282,12 +4282,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4301,7 +4301,7 @@
         <v>126893092</v>
       </c>
       <c r="B37" t="n">
-        <v>97333</v>
+        <v>97320</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Pia Edfors, Caspar Ström, Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Ignacio Alvarez, Christina Boyd, per-erik mukka, Brian Johnson, Carin von Köhler</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4402,7 +4402,7 @@
         <v>126891761</v>
       </c>
       <c r="B38" t="n">
-        <v>105488</v>
+        <v>105471</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>126895021</v>
       </c>
       <c r="B39" t="n">
-        <v>97333</v>
+        <v>97320</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4601,32 +4601,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126896015</v>
+        <v>126896476</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>78678</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>835346</v>
+        <v>835392</v>
       </c>
       <c r="R40" t="n">
-        <v>7431909</v>
+        <v>7431887</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4669,9 +4669,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4686,12 +4696,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4702,32 +4712,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126896476</v>
+        <v>126896015</v>
       </c>
       <c r="B41" t="n">
-        <v>78687</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4737,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>835392</v>
+        <v>835346</v>
       </c>
       <c r="R41" t="n">
-        <v>7431887</v>
+        <v>7431909</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,19 +4780,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4797,12 +4797,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4816,7 +4816,7 @@
         <v>126896012</v>
       </c>
       <c r="B42" t="n">
-        <v>97327</v>
+        <v>97314</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4914,32 +4914,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126896215</v>
+        <v>126896207</v>
       </c>
       <c r="B43" t="n">
-        <v>95306</v>
+        <v>79629</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2387</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>835224</v>
+        <v>835216</v>
       </c>
       <c r="R43" t="n">
-        <v>7431834</v>
+        <v>7432256</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Petra Wikström, Jenny Hjelm Córdoba, Jörgen Sundin, Louise Wolthers, Petya Valcheva, Cecilia Goldkuhl</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5028,7 +5028,7 @@
         <v>126892874</v>
       </c>
       <c r="B44" t="n">
-        <v>75144</v>
+        <v>75135</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Jenny Hjelm Córdoba, Petya Valcheva, Petra Wikström, Jörgen Sundin, Louise Wolthers, Cecilia Goldkuhl, Petya Valcheva, Petra Wikström, Jörgen Sundin, Louise Wolthers, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5126,32 +5126,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126896207</v>
+        <v>126896215</v>
       </c>
       <c r="B45" t="n">
-        <v>79638</v>
+        <v>95293</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>2387</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>835216</v>
+        <v>835224</v>
       </c>
       <c r="R45" t="n">
-        <v>7432256</v>
+        <v>7431834</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Petra Wikström, Jenny Hjelm Córdoba, Jörgen Sundin, Louise Wolthers, Petya Valcheva, Cecilia Goldkuhl</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5240,7 +5240,7 @@
         <v>126896001</v>
       </c>
       <c r="B46" t="n">
-        <v>56855</v>
+        <v>56849</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126896013</v>
+        <v>126891762</v>
       </c>
       <c r="B47" t="n">
-        <v>97333</v>
+        <v>105471</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>835330</v>
+        <v>835361</v>
       </c>
       <c r="R47" t="n">
-        <v>7431947</v>
+        <v>7431869</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5423,12 +5423,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Louise Wolthers, Petya Valcheva, Jörgen Sundin, Petra Wikström, Jenny Hjelm Córdoba</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5439,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126891762</v>
+        <v>126896013</v>
       </c>
       <c r="B48" t="n">
-        <v>105488</v>
+        <v>97320</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5450,21 +5450,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>835361</v>
+        <v>835330</v>
       </c>
       <c r="R48" t="n">
-        <v>7431869</v>
+        <v>7431947</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,12 +5524,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5543,7 +5543,7 @@
         <v>126896453</v>
       </c>
       <c r="B49" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>126896459</v>
       </c>
       <c r="B50" t="n">
-        <v>97333</v>
+        <v>97320</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5762,45 +5762,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126896046</v>
+        <v>126895028</v>
       </c>
       <c r="B51" t="n">
-        <v>82861</v>
+        <v>91247</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>2013</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>835241</v>
+        <v>835423</v>
       </c>
       <c r="R51" t="n">
-        <v>7432287</v>
+        <v>7431886</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5847,12 +5847,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5863,45 +5863,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126895028</v>
+        <v>126896046</v>
       </c>
       <c r="B52" t="n">
-        <v>91260</v>
+        <v>82852</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2013</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>835423</v>
+        <v>835241</v>
       </c>
       <c r="R52" t="n">
-        <v>7431886</v>
+        <v>7432287</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5948,12 +5948,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5964,10 +5964,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126893090</v>
+        <v>126896455</v>
       </c>
       <c r="B53" t="n">
-        <v>92614</v>
+        <v>79629</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5975,21 +5975,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5999,10 +5999,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>835354</v>
+        <v>835445</v>
       </c>
       <c r="R53" t="n">
-        <v>7431995</v>
+        <v>7431926</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6032,9 +6032,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6049,12 +6059,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Pia Edfors, Caspar Ström, Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Ignacio Alvarez, Christina Boyd, per-erik mukka, Brian Johnson, Carin von Köhler</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6065,32 +6075,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126896455</v>
+        <v>126893083</v>
       </c>
       <c r="B54" t="n">
-        <v>79638</v>
+        <v>97314</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6100,10 +6110,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>835445</v>
+        <v>835458</v>
       </c>
       <c r="R54" t="n">
-        <v>7431926</v>
+        <v>7431881</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6133,19 +6143,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6160,12 +6160,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6176,32 +6176,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893083</v>
+        <v>126893090</v>
       </c>
       <c r="B55" t="n">
-        <v>97327</v>
+        <v>92601</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>835458</v>
+        <v>835354</v>
       </c>
       <c r="R55" t="n">
-        <v>7431881</v>
+        <v>7431995</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Pia Edfors, Caspar Ström, Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Ignacio Alvarez, Christina Boyd, per-erik mukka, Brian Johnson, Carin von Köhler</t>
+          <t>Pia Edfors, Carin von Köhler, Brian Johnson, per-erik mukka, Christina Boyd, Ignacio Alvarez, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk, Caspar Ström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6277,10 +6277,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126895019</v>
+        <v>126892870</v>
       </c>
       <c r="B56" t="n">
-        <v>91282</v>
+        <v>57817</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6288,34 +6288,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>112</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Karijoki - Havsvalla, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>835295</v>
+        <v>835300</v>
       </c>
       <c r="R56" t="n">
-        <v>7431936</v>
+        <v>7431922</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6362,12 +6362,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Jenny Hjelm Córdoba, Petya Valcheva, Petra Wikström, Jörgen Sundin, Louise Wolthers, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6378,10 +6378,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126891747</v>
+        <v>126895027</v>
       </c>
       <c r="B57" t="n">
-        <v>80027</v>
+        <v>58027</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6389,34 +6389,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Karijoki - Havsvalla, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>835247</v>
+        <v>835398</v>
       </c>
       <c r="R57" t="n">
-        <v>7432156</v>
+        <v>7431822</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6463,12 +6463,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6479,32 +6479,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126892870</v>
+        <v>126891747</v>
       </c>
       <c r="B58" t="n">
-        <v>57823</v>
+        <v>80018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>6456</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>835300</v>
+        <v>835247</v>
       </c>
       <c r="R58" t="n">
-        <v>7431922</v>
+        <v>7432156</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6564,12 +6564,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6580,32 +6580,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126895027</v>
+        <v>126895019</v>
       </c>
       <c r="B59" t="n">
-        <v>58033</v>
+        <v>91269</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>112</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>835398</v>
+        <v>835295</v>
       </c>
       <c r="R59" t="n">
-        <v>7431822</v>
+        <v>7431936</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6681,32 +6681,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126896035</v>
+        <v>126891218</v>
       </c>
       <c r="B60" t="n">
-        <v>98450</v>
+        <v>92609</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>835290</v>
+        <v>835411</v>
       </c>
       <c r="R60" t="n">
-        <v>7432175</v>
+        <v>7432011</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6766,12 +6766,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6782,10 +6782,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126891218</v>
+        <v>126892867</v>
       </c>
       <c r="B61" t="n">
-        <v>92622</v>
+        <v>56849</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6793,21 +6793,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>835411</v>
+        <v>835268</v>
       </c>
       <c r="R61" t="n">
-        <v>7432011</v>
+        <v>7431964</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6855,6 +6855,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6867,12 +6872,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Christina Boyd, Brian Johnson, per-erik mukka, Carin von Köhler, Linnea Ingelsbo, Caspar Ström, Pia Edfors, Joakim Karlsson, Tomas Falk</t>
+          <t>Jenny Hjelm Córdoba, Petya Valcheva, Petra Wikström, Jörgen Sundin, Louise Wolthers, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6883,32 +6888,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126892867</v>
+        <v>126896035</v>
       </c>
       <c r="B62" t="n">
-        <v>56855</v>
+        <v>98436</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6918,10 +6923,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>835268</v>
+        <v>835290</v>
       </c>
       <c r="R62" t="n">
-        <v>7431964</v>
+        <v>7432175</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6956,11 +6961,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6973,12 +6973,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6992,7 +6992,7 @@
         <v>126896458</v>
       </c>
       <c r="B63" t="n">
-        <v>91282</v>
+        <v>91269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7100,32 +7100,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126894490</v>
+        <v>126892868</v>
       </c>
       <c r="B64" t="n">
-        <v>91493</v>
+        <v>56849</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1503</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>835300</v>
+        <v>835234</v>
       </c>
       <c r="R64" t="n">
-        <v>7431907</v>
+        <v>7431879</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7173,6 +7173,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7185,12 +7190,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Jenny Hjelm Córdoba, Petya Valcheva, Petra Wikström, Jörgen Sundin, Louise Wolthers, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7201,32 +7206,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126896213</v>
+        <v>126894490</v>
       </c>
       <c r="B65" t="n">
-        <v>100605</v>
+        <v>91480</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1365</v>
+        <v>1503</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7236,10 +7241,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>835235</v>
+        <v>835300</v>
       </c>
       <c r="R65" t="n">
-        <v>7431827</v>
+        <v>7431907</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7269,19 +7274,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7296,12 +7291,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Petra Wikström, Jenny Hjelm Córdoba, Jörgen Sundin, Louise Wolthers, Petya Valcheva, Cecilia Goldkuhl</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7312,10 +7307,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126892868</v>
+        <v>126896213</v>
       </c>
       <c r="B66" t="n">
-        <v>56855</v>
+        <v>100591</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7323,21 +7318,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>1365</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7347,10 +7342,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>835234</v>
+        <v>835235</v>
       </c>
       <c r="R66" t="n">
-        <v>7431879</v>
+        <v>7431827</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,14 +7375,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7402,12 +7402,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Petra Wikström, Cecilia Goldkuhl, Petya Valcheva, Louise Wolthers, Jörgen Sundin, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7418,32 +7418,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126896051</v>
+        <v>126894487</v>
       </c>
       <c r="B67" t="n">
-        <v>98367</v>
+        <v>56840</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7453,10 +7453,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>835330</v>
+        <v>835105</v>
       </c>
       <c r="R67" t="n">
-        <v>7432131</v>
+        <v>7432062</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7503,12 +7503,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7519,32 +7519,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126894487</v>
+        <v>126896051</v>
       </c>
       <c r="B68" t="n">
-        <v>56846</v>
+        <v>98353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102612</v>
+        <v>219790</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>835105</v>
+        <v>835330</v>
       </c>
       <c r="R68" t="n">
-        <v>7432062</v>
+        <v>7432131</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7604,12 +7604,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7623,7 +7623,7 @@
         <v>126915007</v>
       </c>
       <c r="B69" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>126915556</v>
       </c>
       <c r="B70" t="n">
-        <v>57823</v>
+        <v>57817</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>126894627</v>
       </c>
       <c r="B71" t="n">
-        <v>79609</v>
+        <v>79600</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>126915557</v>
       </c>
       <c r="B72" t="n">
-        <v>92634</v>
+        <v>92621</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>126894632</v>
       </c>
       <c r="B73" t="n">
-        <v>92815</v>
+        <v>92802</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8117,45 +8117,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126915568</v>
+        <v>126915019</v>
       </c>
       <c r="B74" t="n">
-        <v>92622</v>
+        <v>92802</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>835341</v>
+        <v>835275</v>
       </c>
       <c r="R74" t="n">
-        <v>7432052</v>
+        <v>7432030</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8202,57 +8202,61 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126915019</v>
+        <v>126915568</v>
       </c>
       <c r="B75" t="n">
-        <v>92815</v>
+        <v>92609</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Karijoki, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>835275</v>
+        <v>835341</v>
       </c>
       <c r="R75" t="n">
-        <v>7432030</v>
+        <v>7432052</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8299,26 +8303,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>126915562</v>
       </c>
       <c r="B76" t="n">
-        <v>58033</v>
+        <v>58027</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>126915015</v>
       </c>
       <c r="B77" t="n">
-        <v>79044</v>
+        <v>79035</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>126894633</v>
       </c>
       <c r="B78" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>126915011</v>
       </c>
       <c r="B79" t="n">
-        <v>91282</v>
+        <v>91269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>126915032</v>
       </c>
       <c r="B80" t="n">
-        <v>78426</v>
+        <v>78417</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>126915016</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>79035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8917,48 +8917,51 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126894643</v>
+        <v>126916087</v>
       </c>
       <c r="B82" t="n">
-        <v>92622</v>
+        <v>92635</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>835435</v>
+        <v>835434</v>
       </c>
       <c r="R82" t="n">
-        <v>7431898</v>
+        <v>7431905</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8996,18 +8999,19 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9018,51 +9022,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126916087</v>
+        <v>126894643</v>
       </c>
       <c r="B83" t="n">
-        <v>92648</v>
+        <v>92609</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Karijoki, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>835434</v>
+        <v>835435</v>
       </c>
       <c r="R83" t="n">
-        <v>7431905</v>
+        <v>7431898</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9100,19 +9101,18 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9126,7 +9126,7 @@
         <v>126915017</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>79035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>126927927</v>
       </c>
       <c r="B85" t="n">
-        <v>78778</v>
+        <v>78769</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>126927910</v>
       </c>
       <c r="B86" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>126891792</v>
       </c>
       <c r="B87" t="n">
-        <v>79990</v>
+        <v>79981</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>126927931</v>
       </c>
       <c r="B88" t="n">
-        <v>92622</v>
+        <v>92609</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>126943155</v>
       </c>
       <c r="B89" t="n">
-        <v>78778</v>
+        <v>78769</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
+          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9756,7 +9756,7 @@
         <v>126943164</v>
       </c>
       <c r="B90" t="n">
-        <v>80027</v>
+        <v>80018</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
+          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9857,7 +9857,7 @@
         <v>126943156</v>
       </c>
       <c r="B91" t="n">
-        <v>92622</v>
+        <v>92609</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
+          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9958,7 +9958,7 @@
         <v>126943157</v>
       </c>
       <c r="B92" t="n">
-        <v>77998</v>
+        <v>77989</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
+          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10059,7 +10059,7 @@
         <v>126943160</v>
       </c>
       <c r="B93" t="n">
-        <v>97333</v>
+        <v>97320</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
+          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10160,7 +10160,7 @@
         <v>126943150</v>
       </c>
       <c r="B94" t="n">
-        <v>97333</v>
+        <v>97320</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
+          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10261,7 +10261,7 @@
         <v>126943163</v>
       </c>
       <c r="B95" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
+          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10372,7 +10372,7 @@
         <v>126943159</v>
       </c>
       <c r="B96" t="n">
-        <v>78687</v>
+        <v>78678</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
+          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10473,7 +10473,7 @@
         <v>126943161</v>
       </c>
       <c r="B97" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
+          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10571,32 +10571,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126943153</v>
+        <v>126943151</v>
       </c>
       <c r="B98" t="n">
-        <v>98450</v>
+        <v>92609</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>835440</v>
+        <v>835382</v>
       </c>
       <c r="R98" t="n">
-        <v>7431856</v>
+        <v>7432189</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
+          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10672,32 +10672,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126943151</v>
+        <v>126943153</v>
       </c>
       <c r="B99" t="n">
-        <v>92622</v>
+        <v>98436</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>835382</v>
+        <v>835440</v>
       </c>
       <c r="R99" t="n">
-        <v>7432189</v>
+        <v>7431856</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Tomas Falk, Linnea Ingelsbo, Joakim Karlsson, Christina Boyd, per-erik mukka, Brian Johnson, Pia Edfors, Carin von Köhler, Caspar Ström</t>
+          <t>Caspar Ström, Carin von Köhler, Pia Edfors, Brian Johnson, per-erik mukka, Christina Boyd, Joakim Karlsson, Linnea Ingelsbo, Tomas Falk</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -5240,7 +5240,7 @@
         <v>126896001</v>
       </c>
       <c r="B46" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>126892867</v>
       </c>
       <c r="B62" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>126892868</v>
       </c>
       <c r="B66" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -5240,7 +5240,7 @@
         <v>126896001</v>
       </c>
       <c r="B46" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
+          <t>Cecilia Goldkuhl, Louise Wolthers, Petya Valcheva, Jörgen Sundin, Petra Wikström, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -6886,7 +6886,7 @@
         <v>126892867</v>
       </c>
       <c r="B62" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>126892868</v>
       </c>
       <c r="B66" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -5327,7 +5327,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Louise Wolthers, Petya Valcheva, Jörgen Sundin, Petra Wikström, Jenny Hjelm Córdoba</t>
+          <t>Cecilia Goldkuhl, Jenny Hjelm Córdoba, Petra Wikström, Jörgen Sundin, Petya Valcheva, Louise Wolthers</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -5240,7 +5240,7 @@
         <v>126896001</v>
       </c>
       <c r="B46" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>126892867</v>
       </c>
       <c r="B62" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Jenny Hjelm Córdoba, Petya Valcheva, Petra Wikström, Jörgen Sundin, Louise Wolthers, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7315,7 +7315,7 @@
         <v>126892868</v>
       </c>
       <c r="B66" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
+          <t>Jenny Hjelm Córdoba, Petya Valcheva, Petra Wikström, Jörgen Sundin, Louise Wolthers, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -5240,7 +5240,7 @@
         <v>126896001</v>
       </c>
       <c r="B46" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>126892867</v>
       </c>
       <c r="B62" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Petya Valcheva, Petra Wikström, Jörgen Sundin, Louise Wolthers, Cecilia Goldkuhl</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7315,7 +7315,7 @@
         <v>126892868</v>
       </c>
       <c r="B66" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Petya Valcheva, Petra Wikström, Jörgen Sundin, Louise Wolthers, Cecilia Goldkuhl</t>
+          <t>Jenny Hjelm Córdoba, Cecilia Goldkuhl, Louise Wolthers, Jörgen Sundin, Petra Wikström, Petya Valcheva</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">

--- a/artfynd/A 37735-2025 artfynd.xlsx
+++ b/artfynd/A 37735-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY159"/>
+  <dimension ref="A1:AZ159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126895042</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126895043</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126895044</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896048</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896172</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891211</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891745</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126895019</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126895020</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1674,6 +1724,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896156</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1785,6 +1840,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896458</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915011</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1992,6 +2057,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017333</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2103,6 +2173,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896478</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2204,6 +2279,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891788</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2306,6 +2386,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893107</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2407,6 +2492,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893108</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2518,6 +2608,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896476</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2629,6 +2724,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896477</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2730,6 +2830,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915030</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2829,6 +2934,11 @@
       <c r="AY22" t="inlineStr">
         <is>
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126943159</t>
         </is>
       </c>
     </row>
@@ -2956,6 +3066,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891792</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3057,6 +3172,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891751</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3158,6 +3278,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927926</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3259,6 +3384,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891779</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3360,6 +3490,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891780</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3461,6 +3596,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891781</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3562,6 +3702,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896046</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3673,6 +3818,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896220</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3784,6 +3934,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896222</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3885,6 +4040,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891212</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3986,6 +4146,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126892876</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4087,6 +4252,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896019</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4196,6 +4366,11 @@
       <c r="AY35" t="inlineStr">
         <is>
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896213</t>
         </is>
       </c>
     </row>
@@ -4309,6 +4484,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131120510</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4410,6 +4590,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891767</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4511,6 +4696,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126894490</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4612,6 +4802,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126895037</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4713,6 +4908,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126895028</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4814,6 +5014,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126894632</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4915,6 +5120,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126895024</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5016,6 +5226,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915019</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5117,6 +5332,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896023</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5228,6 +5448,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896215</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5329,6 +5554,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915024</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5430,6 +5660,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896055</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5531,6 +5766,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126943152</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5632,6 +5872,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891725</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5738,6 +5983,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017334</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5839,6 +6089,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893090</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5945,6 +6200,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414788</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6051,6 +6311,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017335</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6157,6 +6422,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414787</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6258,6 +6528,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891218</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6359,6 +6634,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891965</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6460,6 +6740,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893109</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6561,6 +6846,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126894504</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6662,6 +6952,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126894505</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6763,6 +7058,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126894643</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6864,6 +7164,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126895046</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6965,6 +7270,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126895047</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7066,6 +7376,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896052</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7167,6 +7482,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927931</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7268,6 +7588,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126943151</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7369,6 +7694,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126943156</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7470,6 +7800,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893081</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7571,6 +7906,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891955</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7672,6 +8012,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891743</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7771,6 +8116,11 @@
       <c r="AY70" t="inlineStr">
         <is>
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126895016</t>
         </is>
       </c>
     </row>
@@ -7878,6 +8228,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916087</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7979,6 +8334,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891775</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8080,6 +8440,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126894498</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8191,6 +8556,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896221</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8292,6 +8662,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126943161</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8393,6 +8768,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896015</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8494,6 +8874,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915015</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8595,6 +8980,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915016</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8696,6 +9086,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915017</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8797,6 +9192,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915032</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8898,6 +9298,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891727</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8999,6 +9404,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891733</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9100,6 +9510,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126892874</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9211,6 +9626,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896211</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9312,6 +9732,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927908</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9423,6 +9848,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896462</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9524,6 +9954,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927927</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9625,6 +10060,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126943155</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9726,6 +10166,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891737</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9827,6 +10272,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893073</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9928,6 +10378,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126894477</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10039,6 +10494,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896207</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10150,6 +10610,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896453</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10261,6 +10726,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896454</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10372,6 +10842,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896455</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10483,6 +10958,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896456</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10584,6 +11064,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915007</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10685,6 +11170,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927910</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10786,6 +11276,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891747</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10887,6 +11382,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126943164</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10988,6 +11488,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893080</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11089,6 +11594,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126943157</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11186,6 +11696,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045736</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11287,6 +11802,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891741</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11393,6 +11913,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126892865</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11504,6 +12029,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126943163</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11601,6 +12131,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045729</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11707,6 +12242,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126892867</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11813,6 +12353,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126892868</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11914,6 +12459,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896001</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12015,6 +12565,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126894487</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12116,6 +12671,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891959</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12217,6 +12777,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126895027</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12318,6 +12883,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891742</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12419,6 +12989,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891954</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12520,6 +13095,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126892870</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12621,6 +13201,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126895018</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12732,6 +13317,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896216</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12833,6 +13423,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126943158</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12934,6 +13529,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896010</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13035,6 +13635,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891217</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13136,6 +13741,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891786</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13237,6 +13847,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126892879</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13338,6 +13953,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126892880</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13439,6 +14059,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126894503</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13540,6 +14165,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896051</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13641,6 +14271,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927930</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13742,6 +14377,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893099</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13843,6 +14483,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893100</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13944,6 +14589,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896033</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14045,6 +14695,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896034</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14146,6 +14801,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896035</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14247,6 +14907,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126943153</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14348,6 +15013,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891761</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14449,6 +15119,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891762</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14550,6 +15225,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896044</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14651,6 +15331,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126895994</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14752,6 +15437,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891752</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14853,6 +15543,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126892873</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14954,6 +15649,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893087</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15055,6 +15755,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893092</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15156,6 +15861,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126894482</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15257,6 +15967,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126895021</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15358,6 +16073,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896013</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15469,6 +16189,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896208</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15580,6 +16305,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896459</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15691,6 +16421,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896460</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15792,6 +16527,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126943150</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15893,6 +16633,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126943160</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15994,6 +16739,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893082</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16095,6 +16845,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893083</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16196,6 +16951,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893085</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16297,6 +17057,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896012</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16398,6 +17163,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891756</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16499,6 +17269,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891753</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16600,6 +17375,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126894633</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16711,6 +17491,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126896461</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16812,6 +17597,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126894489</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16913,8 +17703,173 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126894627</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>